--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -548,7 +548,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3888.5</v>
+        <v>3944.67</v>
       </c>
     </row>
     <row r="5">
@@ -564,7 +564,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3379.5</v>
+        <v>3277.6</v>
       </c>
     </row>
     <row r="7">
@@ -580,7 +580,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>2400.17</v>
+        <v>2086.88</v>
       </c>
     </row>
     <row r="9">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -172,6 +172,21 @@
     <t xml:space="preserve">11/4/2024</t>
   </si>
   <si>
+    <t xml:space="preserve">24-394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/30/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/22/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">23-6573</t>
   </si>
   <si>
@@ -182,15 +197,6 @@
   </si>
   <si>
     <t xml:space="preserve">1/21/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisconsin Bell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/21/2025</t>
   </si>
 </sst>
 </file>
@@ -540,7 +546,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>5987.3</v>
+        <v>5758.64</v>
       </c>
     </row>
     <row r="4">
@@ -556,7 +562,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3541.25</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="6">
@@ -572,7 +578,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>3814.29</v>
+        <v>3824.88</v>
       </c>
     </row>
     <row r="8">
@@ -580,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>2086.88</v>
+        <v>2525.33</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +594,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>3414.6</v>
+        <v>3888.17</v>
       </c>
     </row>
     <row r="10">
@@ -881,52 +887,52 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
       </c>
       <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="D5" t="n">
-        <v>87</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>54</v>
       </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5"/>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D6" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>51</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G6"/>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -163,6 +163,18 @@
     <t xml:space="preserve">11/22/2024</t>
   </si>
   <si>
+    <t xml:space="preserve">24-304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/29/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/5/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">23-167</t>
   </si>
   <si>
@@ -185,18 +197,6 @@
   </si>
   <si>
     <t xml:space="preserve">5/22/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-6573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concurrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/21/2025</t>
   </si>
 </sst>
 </file>
@@ -546,7 +546,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>5758.64</v>
+        <v>5050.73</v>
       </c>
     </row>
     <row r="4">
@@ -554,7 +554,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3944.67</v>
+        <v>3907.4</v>
       </c>
     </row>
     <row r="5">
@@ -562,7 +562,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3374</v>
+        <v>3446.55</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3277.6</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="7">
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>2525.33</v>
+        <v>2441.4</v>
       </c>
     </row>
     <row r="9">
@@ -602,7 +602,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>3327.9</v>
+        <v>2912.5</v>
       </c>
     </row>
   </sheetData>
@@ -869,20 +869,22 @@
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
         <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4"/>
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -890,47 +892,47 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5" t="s">
         <v>55</v>
-      </c>
-      <c r="H5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>58</v>
       </c>
-      <c r="D6" t="n">
-        <v>87</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>59</v>
       </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6"/>
       <c r="H6" t="s">
         <v>60</v>
       </c>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -538,7 +538,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>3414</v>
+        <v>3595.67</v>
       </c>
     </row>
     <row r="3">
@@ -546,7 +546,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>5050.73</v>
+        <v>4761.71</v>
       </c>
     </row>
     <row r="4">
@@ -562,7 +562,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3446.55</v>
+        <v>3194.43</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>3824.88</v>
+        <v>3584.45</v>
       </c>
     </row>
     <row r="8">
@@ -594,7 +594,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>3888.17</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="10">
@@ -602,7 +602,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>2912.5</v>
+        <v>2844</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -538,7 +538,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>3595.67</v>
+        <v>4944.17</v>
       </c>
     </row>
     <row r="3">
@@ -546,7 +546,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4761.71</v>
+        <v>4888.73</v>
       </c>
     </row>
     <row r="4">
@@ -554,7 +554,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3907.4</v>
+        <v>4334.5</v>
       </c>
     </row>
     <row r="5">
@@ -562,7 +562,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3194.43</v>
+        <v>2982.63</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3476</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>3584.45</v>
+        <v>3845.13</v>
       </c>
     </row>
     <row r="8">
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>2441.4</v>
+        <v>3466.85</v>
       </c>
     </row>
     <row r="9">
@@ -594,7 +594,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>3677</v>
+        <v>3663.58</v>
       </c>
     </row>
     <row r="10">
@@ -602,7 +602,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>2844</v>
+        <v>3262.65</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -9,12 +9,13 @@
     <sheet name="average_opinion_lengthsjustice" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="longest_opinions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="shortest_opinions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="combined_opinion_lengths" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -109,6 +110,21 @@
     <t xml:space="preserve">4/2/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">23-477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrmetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/4/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/18/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">23-365</t>
   </si>
   <si>
@@ -121,82 +137,412 @@
     <t xml:space="preserve">10/15/2024</t>
   </si>
   <si>
-    <t xml:space="preserve">23-852</t>
+    <t xml:space="preserve">Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/13/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/11/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/6/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/22/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/29/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/30/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/22/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-6573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/21/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_opinions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_authors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Kagan; Roberts; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Sotomayor; Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">Vanderstok</t>
   </si>
   <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/8/2024</t>
+    <t xml:space="preserve">Alito; Gorsuch; Jackson; Kavanaugh; Sotomayor; Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">3/26/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/13/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/11/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facebook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/6/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/22/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laboratory Corp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/29/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/5/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-167</t>
+    <t xml:space="preserve">Barrett; Jackson; Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/20/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kouisisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Gorsuch; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Gorsuch; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/22/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kavanaugh; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esteras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Jackson; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McLaughlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bufkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delligatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/21/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calumet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perttu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF v. EPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> R.J. Reynolds </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/29/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Per Curiam; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wisconsin Bell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/21/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Kavanaugh; Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/16/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Per Curiam; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/17/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kavanaugh; Per Curiam; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willaims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.J.T.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Canin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/15/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOE v. CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kagan; Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith and Wesson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kagan; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cunningham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/17/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOM Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/15/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parrish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waetzig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/26/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Jackson; Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC/Devas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouarafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/10/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dewberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.M.D. Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Per Curiam</t>
   </si>
   <si>
     <t xml:space="preserve">Hamm</t>
   </si>
   <si>
     <t xml:space="preserve">11/4/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drummond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4-4)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/30/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/22/2025</t>
   </si>
 </sst>
 </file>
@@ -562,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>2982.63</v>
+        <v>3148.28</v>
       </c>
     </row>
     <row r="6">
@@ -594,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>3663.58</v>
+        <v>3996.55</v>
       </c>
     </row>
     <row r="10">
@@ -699,77 +1045,77 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>9621</v>
+        <v>9967</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>8325</v>
+        <v>9621</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>8036</v>
+        <v>8325</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -898,43 +1244,1214 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
         <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5"/>
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34738</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="n">
+        <v>25575</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17985</v>
+      </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17663</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17215</v>
+      </c>
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15972</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15479</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14815</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14496</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13263</v>
+      </c>
+      <c r="F11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12801</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12543</v>
+      </c>
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11347</v>
+      </c>
+      <c r="F16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11132</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="n">
+        <v>11021</v>
+      </c>
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10616</v>
+      </c>
+      <c r="F19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10542</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10289</v>
+      </c>
+      <c r="F21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9964</v>
+      </c>
+      <c r="F22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9908</v>
+      </c>
+      <c r="F23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9846</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9098</v>
+      </c>
+      <c r="F25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8932</v>
+      </c>
+      <c r="F26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8137</v>
+      </c>
+      <c r="F27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7157</v>
+      </c>
+      <c r="F28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7119</v>
+      </c>
+      <c r="F29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7109</v>
+      </c>
+      <c r="F30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7003</v>
+      </c>
+      <c r="F31" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6844</v>
+      </c>
+      <c r="F32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6795</v>
+      </c>
+      <c r="F33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6651</v>
+      </c>
+      <c r="F34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6257</v>
+      </c>
+      <c r="F37" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6214</v>
+      </c>
+      <c r="F38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5605</v>
+      </c>
+      <c r="F39" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5528</v>
+      </c>
+      <c r="F40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5310</v>
+      </c>
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>156</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4826</v>
+      </c>
+      <c r="F43" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4788</v>
+      </c>
+      <c r="F44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>160</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4212</v>
+      </c>
+      <c r="F45" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4075</v>
+      </c>
+      <c r="F46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>163</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3963</v>
+      </c>
+      <c r="F47" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" t="s">
+        <v>28</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3927</v>
+      </c>
+      <c r="F48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3800</v>
+      </c>
+      <c r="F49" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3572</v>
+      </c>
+      <c r="F50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>168</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3472</v>
+      </c>
+      <c r="F51" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3342</v>
+      </c>
+      <c r="F52" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2458</v>
+      </c>
+      <c r="F53" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
         <v>40</v>
       </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D55" t="s">
         <v>40</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E55" t="n">
+        <v>449</v>
+      </c>
+      <c r="F55" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>40</v>
+      </c>
+      <c r="D56" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" t="n">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F56" t="s">
         <v>57</v>
       </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" t="s">
-        <v>60</v>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>40</v>
+      </c>
+      <c r="D57" t="s">
+        <v>40</v>
+      </c>
+      <c r="E57" t="n">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" t="s">
+        <v>40</v>
+      </c>
+      <c r="E58" t="n">
+        <v>14</v>
+      </c>
+      <c r="F58" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -170,6 +170,9 @@
     <t xml:space="preserve">Laboratory Corp.</t>
   </si>
   <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">4/29/2025</t>
   </si>
   <si>
@@ -447,9 +450,6 @@
   </si>
   <si>
     <t xml:space="preserve">Gorsuch; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
   </si>
   <si>
     <t xml:space="preserve">DOE v. CA</t>
@@ -1224,13 +1224,13 @@
         <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -1238,7 +1238,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -1247,16 +1247,16 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -1264,23 +1264,23 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6"/>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1296,19 +1296,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
         <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
         <v>18</v>
@@ -1322,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1342,7 +1342,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -1356,22 +1356,22 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
         <v>17985</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -1382,7 +1382,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
         <v>38</v>
@@ -1396,33 +1396,33 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
         <v>17215</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -1431,18 +1431,18 @@
         <v>15972</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -1451,18 +1451,18 @@
         <v>15479</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1482,7 +1482,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -1496,53 +1496,53 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
         <v>13263</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E12" t="n">
         <v>12801</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
         <v>28</v>
@@ -1551,18 +1551,18 @@
         <v>12543</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
         <v>33</v>
@@ -1571,18 +1571,18 @@
         <v>12000</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
@@ -1591,61 +1591,61 @@
         <v>11500</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
         <v>11347</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
         <v>11132</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
         <v>11021</v>
@@ -1656,33 +1656,33 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E19" t="n">
         <v>10616</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
         <v>38</v>
@@ -1696,13 +1696,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
         <v>38</v>
@@ -1711,18 +1711,18 @@
         <v>10289</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
@@ -1731,21 +1731,21 @@
         <v>9964</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23" t="n">
         <v>9908</v>
@@ -1756,73 +1756,73 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B24" t="n">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E24" t="n">
         <v>9846</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E25" t="n">
         <v>9098</v>
       </c>
       <c r="F25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E26" t="n">
         <v>8932</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
         <v>28</v>
@@ -1831,38 +1831,38 @@
         <v>8137</v>
       </c>
       <c r="F27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
         <v>7157</v>
       </c>
       <c r="F28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
@@ -1871,18 +1871,18 @@
         <v>7119</v>
       </c>
       <c r="F29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B30" t="n">
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
         <v>28</v>
@@ -1891,32 +1891,32 @@
         <v>7109</v>
       </c>
       <c r="F30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E31" t="n">
         <v>7003</v>
       </c>
       <c r="F31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -1931,18 +1931,18 @@
         <v>6844</v>
       </c>
       <c r="F32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D33" t="s">
         <v>38</v>
@@ -1951,18 +1951,18 @@
         <v>6795</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
         <v>28</v>
@@ -1971,12 +1971,12 @@
         <v>6651</v>
       </c>
       <c r="F34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -1991,27 +1991,27 @@
         <v>6487</v>
       </c>
       <c r="F35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B36" t="n">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="E36" t="n">
         <v>6461</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
@@ -2042,7 +2042,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
         <v>28</v>
@@ -2051,7 +2051,7 @@
         <v>6214</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
@@ -2065,13 +2065,13 @@
         <v>150</v>
       </c>
       <c r="D39" t="s">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="E39" t="n">
         <v>5605</v>
       </c>
       <c r="F39" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40">
@@ -2091,7 +2091,7 @@
         <v>5528</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
@@ -2102,7 +2102,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
         <v>28</v>
@@ -2122,7 +2122,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D42" t="s">
         <v>28</v>
@@ -2131,7 +2131,7 @@
         <v>5310</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
@@ -2142,7 +2142,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
         <v>28</v>
@@ -2165,13 +2165,13 @@
         <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="E44" t="n">
         <v>4788</v>
       </c>
       <c r="F44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45">
@@ -2202,10 +2202,10 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E46" t="n">
         <v>4075</v>
@@ -2231,7 +2231,7 @@
         <v>3963</v>
       </c>
       <c r="F47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48">
@@ -2251,7 +2251,7 @@
         <v>3927</v>
       </c>
       <c r="F48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49">
@@ -2271,7 +2271,7 @@
         <v>3800</v>
       </c>
       <c r="F49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50">
@@ -2291,7 +2291,7 @@
         <v>3572</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51">
@@ -2342,7 +2342,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
         <v>28</v>
@@ -2351,7 +2351,7 @@
         <v>2458</v>
       </c>
       <c r="F53" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54">
@@ -2365,13 +2365,13 @@
         <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E54" t="n">
         <v>1700</v>
       </c>
       <c r="F54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
@@ -2396,7 +2396,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" t="n">
         <v>1</v>
@@ -2405,13 +2405,13 @@
         <v>40</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E56" t="n">
         <v>23</v>
       </c>
       <c r="F56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Glossip</t>
   </si>
   <si>
-    <t xml:space="preserve">(6-2)</t>
+    <t xml:space="preserve">(5-3)</t>
   </si>
   <si>
     <t xml:space="preserve">10/9/2024</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">6/20/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Kouisisis</t>
+    <t xml:space="preserve">Kousisis</t>
   </si>
   <si>
     <t xml:space="preserve">Barrett; Gorsuch; Sotomayor; Thomas</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">Jackson; Kavanaugh; Per Curiam; Sotomayor</t>
   </si>
   <si>
-    <t xml:space="preserve">(6-3)*</t>
+    <t xml:space="preserve">(5-4)*</t>
   </si>
   <si>
     <t xml:space="preserve">4/7/2025</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">Hungary</t>
   </si>
   <si>
-    <t xml:space="preserve">Willaims</t>
+    <t xml:space="preserve">Williams</t>
   </si>
   <si>
     <t xml:space="preserve">Kavanaugh; Thomas</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">CC/Devas</t>
   </si>
   <si>
-    <t xml:space="preserve">Bouarafa</t>
+    <t xml:space="preserve">Bouarfa</t>
   </si>
   <si>
     <t xml:space="preserve">12/10/2024</t>
@@ -1445,7 +1445,7 @@
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
         <v>15479</v>
@@ -1725,7 +1725,7 @@
         <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
         <v>9964</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -452,6 +452,9 @@
     <t xml:space="preserve">Gorsuch; Jackson</t>
   </si>
   <si>
+    <t xml:space="preserve">Ames</t>
+  </si>
+  <si>
     <t xml:space="preserve">DOE v. CA</t>
   </si>
   <si>
@@ -459,9 +462,6 @@
   </si>
   <si>
     <t xml:space="preserve">4/4/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ames</t>
   </si>
   <si>
     <t xml:space="preserve">Zuch</t>
@@ -884,7 +884,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4944.17</v>
+        <v>4880.67</v>
       </c>
     </row>
     <row r="3">
@@ -892,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4888.73</v>
+        <v>4811.14</v>
       </c>
     </row>
     <row r="4">
@@ -900,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>4334.5</v>
+        <v>4277.58</v>
       </c>
     </row>
     <row r="5">
@@ -908,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3148.28</v>
+        <v>3094.5</v>
       </c>
     </row>
     <row r="6">
@@ -916,7 +916,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3309</v>
+        <v>3258.38</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +924,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>3845.13</v>
+        <v>3786.07</v>
       </c>
     </row>
     <row r="8">
@@ -932,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>3466.85</v>
+        <v>3416.77</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>3996.55</v>
+        <v>3945.73</v>
       </c>
     </row>
     <row r="10">
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>3262.65</v>
+        <v>3206.7</v>
       </c>
     </row>
   </sheetData>
@@ -999,7 +999,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>14532</v>
+        <v>14227</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -1025,7 +1025,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>14299</v>
+        <v>14114</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
@@ -1051,7 +1051,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>9967</v>
+        <v>9804</v>
       </c>
       <c r="E4" t="s">
         <v>32</v>
@@ -1077,7 +1077,7 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>9621</v>
+        <v>9368</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -1103,7 +1103,7 @@
         <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>8325</v>
+        <v>8172</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -1166,7 +1166,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>42</v>
@@ -1192,7 +1192,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>46</v>
@@ -1218,7 +1218,7 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>50</v>
@@ -1244,7 +1244,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
         <v>55</v>
@@ -1270,7 +1270,7 @@
         <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
@@ -1328,7 +1328,7 @@
         <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>34738</v>
+        <v>34211</v>
       </c>
       <c r="F2" t="s">
         <v>35</v>
@@ -1348,7 +1348,7 @@
         <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>25575</v>
+        <v>24979</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
@@ -1368,7 +1368,7 @@
         <v>62</v>
       </c>
       <c r="E4" t="n">
-        <v>17985</v>
+        <v>17728</v>
       </c>
       <c r="F4" t="s">
         <v>72</v>
@@ -1388,7 +1388,7 @@
         <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>17663</v>
+        <v>17382</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
@@ -1408,7 +1408,7 @@
         <v>76</v>
       </c>
       <c r="E6" t="n">
-        <v>17215</v>
+        <v>16968</v>
       </c>
       <c r="F6" t="s">
         <v>77</v>
@@ -1428,7 +1428,7 @@
         <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>15972</v>
+        <v>15724</v>
       </c>
       <c r="F7" t="s">
         <v>58</v>
@@ -1448,7 +1448,7 @@
         <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>15479</v>
+        <v>15239</v>
       </c>
       <c r="F8" t="s">
         <v>82</v>
@@ -1468,7 +1468,7 @@
         <v>33</v>
       </c>
       <c r="E9" t="n">
-        <v>14815</v>
+        <v>14545</v>
       </c>
       <c r="F9" t="s">
         <v>35</v>
@@ -1488,7 +1488,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>14496</v>
+        <v>14309</v>
       </c>
       <c r="F10" t="s">
         <v>30</v>
@@ -1508,7 +1508,7 @@
         <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>13263</v>
+        <v>13064</v>
       </c>
       <c r="F11" t="s">
         <v>77</v>
@@ -1528,7 +1528,7 @@
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>12801</v>
+        <v>12658</v>
       </c>
       <c r="F12" t="s">
         <v>77</v>
@@ -1548,7 +1548,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>12543</v>
+        <v>12409</v>
       </c>
       <c r="F13" t="s">
         <v>77</v>
@@ -1568,7 +1568,7 @@
         <v>33</v>
       </c>
       <c r="E14" t="n">
-        <v>12000</v>
+        <v>11838</v>
       </c>
       <c r="F14" t="s">
         <v>77</v>
@@ -1588,7 +1588,7 @@
         <v>28</v>
       </c>
       <c r="E15" t="n">
-        <v>11500</v>
+        <v>11345</v>
       </c>
       <c r="F15" t="s">
         <v>53</v>
@@ -1608,7 +1608,7 @@
         <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>11347</v>
+        <v>11109</v>
       </c>
       <c r="F16" t="s">
         <v>99</v>
@@ -1628,7 +1628,7 @@
         <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>11132</v>
+        <v>10951</v>
       </c>
       <c r="F17" t="s">
         <v>102</v>
@@ -1648,7 +1648,7 @@
         <v>62</v>
       </c>
       <c r="E18" t="n">
-        <v>11021</v>
+        <v>10804</v>
       </c>
       <c r="F18" t="s">
         <v>35</v>
@@ -1668,7 +1668,7 @@
         <v>62</v>
       </c>
       <c r="E19" t="n">
-        <v>10616</v>
+        <v>10468</v>
       </c>
       <c r="F19" t="s">
         <v>52</v>
@@ -1688,7 +1688,7 @@
         <v>38</v>
       </c>
       <c r="E20" t="n">
-        <v>10542</v>
+        <v>10417</v>
       </c>
       <c r="F20" t="s">
         <v>35</v>
@@ -1708,7 +1708,7 @@
         <v>38</v>
       </c>
       <c r="E21" t="n">
-        <v>10289</v>
+        <v>10169</v>
       </c>
       <c r="F21" t="s">
         <v>57</v>
@@ -1728,7 +1728,7 @@
         <v>38</v>
       </c>
       <c r="E22" t="n">
-        <v>9964</v>
+        <v>9856</v>
       </c>
       <c r="F22" t="s">
         <v>111</v>
@@ -1748,7 +1748,7 @@
         <v>62</v>
       </c>
       <c r="E23" t="n">
-        <v>9908</v>
+        <v>9763</v>
       </c>
       <c r="F23" t="s">
         <v>24</v>
@@ -1768,7 +1768,7 @@
         <v>62</v>
       </c>
       <c r="E24" t="n">
-        <v>9846</v>
+        <v>9694</v>
       </c>
       <c r="F24" t="s">
         <v>77</v>
@@ -1788,7 +1788,7 @@
         <v>117</v>
       </c>
       <c r="E25" t="n">
-        <v>9098</v>
+        <v>8975</v>
       </c>
       <c r="F25" t="s">
         <v>118</v>
@@ -1808,7 +1808,7 @@
         <v>62</v>
       </c>
       <c r="E26" t="n">
-        <v>8932</v>
+        <v>8767</v>
       </c>
       <c r="F26" t="s">
         <v>63</v>
@@ -1828,7 +1828,7 @@
         <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>8137</v>
+        <v>8021</v>
       </c>
       <c r="F27" t="s">
         <v>122</v>
@@ -1848,7 +1848,7 @@
         <v>62</v>
       </c>
       <c r="E28" t="n">
-        <v>7157</v>
+        <v>7084</v>
       </c>
       <c r="F28" t="s">
         <v>125</v>
@@ -1868,7 +1868,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>7119</v>
+        <v>7036</v>
       </c>
       <c r="F29" t="s">
         <v>128</v>
@@ -1888,7 +1888,7 @@
         <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>7109</v>
+        <v>6988</v>
       </c>
       <c r="F30" t="s">
         <v>131</v>
@@ -1908,7 +1908,7 @@
         <v>134</v>
       </c>
       <c r="E31" t="n">
-        <v>7003</v>
+        <v>6886</v>
       </c>
       <c r="F31" t="s">
         <v>135</v>
@@ -1928,7 +1928,7 @@
         <v>28</v>
       </c>
       <c r="E32" t="n">
-        <v>6844</v>
+        <v>6771</v>
       </c>
       <c r="F32" t="s">
         <v>122</v>
@@ -1948,7 +1948,7 @@
         <v>38</v>
       </c>
       <c r="E33" t="n">
-        <v>6795</v>
+        <v>6675</v>
       </c>
       <c r="F33" t="s">
         <v>122</v>
@@ -1968,7 +1968,7 @@
         <v>28</v>
       </c>
       <c r="E34" t="n">
-        <v>6651</v>
+        <v>6571</v>
       </c>
       <c r="F34" t="s">
         <v>128</v>
@@ -1988,7 +1988,7 @@
         <v>28</v>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>6398</v>
       </c>
       <c r="F35" t="s">
         <v>142</v>
@@ -2008,7 +2008,7 @@
         <v>51</v>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6346</v>
       </c>
       <c r="F36" t="s">
         <v>72</v>
@@ -2019,39 +2019,39 @@
         <v>145</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E37" t="n">
-        <v>6257</v>
+        <v>6156</v>
       </c>
       <c r="F37" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6142</v>
+      </c>
+      <c r="F38" t="s">
         <v>148</v>
-      </c>
-      <c r="B38" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" t="n">
-        <v>6214</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="39">
@@ -2068,7 +2068,7 @@
         <v>51</v>
       </c>
       <c r="E39" t="n">
-        <v>5605</v>
+        <v>5504</v>
       </c>
       <c r="F39" t="s">
         <v>128</v>
@@ -2088,7 +2088,7 @@
         <v>28</v>
       </c>
       <c r="E40" t="n">
-        <v>5528</v>
+        <v>5446</v>
       </c>
       <c r="F40" t="s">
         <v>53</v>
@@ -2108,7 +2108,7 @@
         <v>28</v>
       </c>
       <c r="E41" t="n">
-        <v>5500</v>
+        <v>5438</v>
       </c>
       <c r="F41" t="s">
         <v>154</v>
@@ -2128,7 +2128,7 @@
         <v>28</v>
       </c>
       <c r="E42" t="n">
-        <v>5310</v>
+        <v>5260</v>
       </c>
       <c r="F42" t="s">
         <v>53</v>
@@ -2148,7 +2148,7 @@
         <v>28</v>
       </c>
       <c r="E43" t="n">
-        <v>4826</v>
+        <v>4756</v>
       </c>
       <c r="F43" t="s">
         <v>157</v>
@@ -2168,7 +2168,7 @@
         <v>51</v>
       </c>
       <c r="E44" t="n">
-        <v>4788</v>
+        <v>4724</v>
       </c>
       <c r="F44" t="s">
         <v>128</v>
@@ -2188,7 +2188,7 @@
         <v>28</v>
       </c>
       <c r="E45" t="n">
-        <v>4212</v>
+        <v>4151</v>
       </c>
       <c r="F45" t="s">
         <v>161</v>
@@ -2208,7 +2208,7 @@
         <v>117</v>
       </c>
       <c r="E46" t="n">
-        <v>4075</v>
+        <v>3988</v>
       </c>
       <c r="F46" t="s">
         <v>35</v>
@@ -2228,7 +2228,7 @@
         <v>28</v>
       </c>
       <c r="E47" t="n">
-        <v>3963</v>
+        <v>3908</v>
       </c>
       <c r="F47" t="s">
         <v>128</v>
@@ -2248,7 +2248,7 @@
         <v>28</v>
       </c>
       <c r="E48" t="n">
-        <v>3927</v>
+        <v>3835</v>
       </c>
       <c r="F48" t="s">
         <v>102</v>
@@ -2268,7 +2268,7 @@
         <v>28</v>
       </c>
       <c r="E49" t="n">
-        <v>3800</v>
+        <v>3748</v>
       </c>
       <c r="F49" t="s">
         <v>128</v>
@@ -2288,7 +2288,7 @@
         <v>28</v>
       </c>
       <c r="E50" t="n">
-        <v>3572</v>
+        <v>3523</v>
       </c>
       <c r="F50" t="s">
         <v>53</v>
@@ -2308,7 +2308,7 @@
         <v>28</v>
       </c>
       <c r="E51" t="n">
-        <v>3472</v>
+        <v>3401</v>
       </c>
       <c r="F51" t="s">
         <v>169</v>
@@ -2328,7 +2328,7 @@
         <v>28</v>
       </c>
       <c r="E52" t="n">
-        <v>3342</v>
+        <v>3264</v>
       </c>
       <c r="F52" t="s">
         <v>161</v>
@@ -2348,7 +2348,7 @@
         <v>28</v>
       </c>
       <c r="E53" t="n">
-        <v>2458</v>
+        <v>2413</v>
       </c>
       <c r="F53" t="s">
         <v>142</v>
@@ -2368,7 +2368,7 @@
         <v>51</v>
       </c>
       <c r="E54" t="n">
-        <v>1700</v>
+        <v>1680</v>
       </c>
       <c r="F54" t="s">
         <v>53</v>
@@ -2388,7 +2388,7 @@
         <v>40</v>
       </c>
       <c r="E55" t="n">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="F55" t="s">
         <v>175</v>
@@ -2408,7 +2408,7 @@
         <v>56</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F56" t="s">
         <v>58</v>
@@ -2428,7 +2428,7 @@
         <v>40</v>
       </c>
       <c r="E57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F57" t="s">
         <v>44</v>
@@ -2448,7 +2448,7 @@
         <v>40</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F58" t="s">
         <v>48</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -110,273 +110,330 @@
     <t xml:space="preserve">4/2/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">23-477</t>
+    <t xml:space="preserve">24-316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/21/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/27/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahmoud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/22/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/13/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/11/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/6/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/22/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/29/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/30/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/22/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special Concurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/25/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/18/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_opinions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_authors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_words</t>
   </si>
   <si>
     <t xml:space="preserve">Skrmetti</t>
   </si>
   <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/4/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/18/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-365</t>
+    <t xml:space="preserve">Alito; Barrett; Kagan; Roberts; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumers' Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Kagan; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderstok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Gorsuch; Jackson; Kavanaugh; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/26/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Medical Marijuana</t>
   </si>
   <si>
+    <t xml:space="preserve">Barrett; Jackson; Kavanaugh; Thomas</t>
+  </si>
+  <si>
     <t xml:space="preserve">(5-4)</t>
   </si>
   <si>
-    <t xml:space="preserve">10/15/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/13/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/11/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facebook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/6/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/22/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laboratory Corp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/29/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/5/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drummond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4-4)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/30/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/22/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-6573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concurrence</t>
+    <t xml:space="preserve">Free Speech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kousisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Gorsuch; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/26/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Gorsuch; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/20/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guitierrez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hewitt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kavanaugh; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bufkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delligatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/21/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esteras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Jackson; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calumet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McLaughlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF v. EPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perttu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/29/2025</t>
   </si>
   <si>
     <t xml:space="preserve">Andrew</t>
   </si>
   <si>
-    <t xml:space="preserve">(7-2)</t>
+    <t xml:space="preserve">Alito; Per Curiam; Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">1/21/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">case_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_opinions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_authors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett; Kagan; Roberts; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanderstok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Gorsuch; Jackson; Kavanaugh; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/26/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Jackson; Kavanaugh; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stanley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Jackson; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/20/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kousisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Gorsuch; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velazquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett; Gorsuch; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/22/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Kavanaugh; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esteras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett; Jackson; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuld</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McLaughlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catholic Charities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bufkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/5/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delligatti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/21/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calumet </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perttu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feliciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF v. EPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/4/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lackey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Roberts</t>
-  </si>
-  <si>
     <t xml:space="preserve"> R.J. Reynolds </t>
   </si>
   <si>
-    <t xml:space="preserve">Seven County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/29/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Per Curiam; Thomas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wisconsin Bell</t>
   </si>
   <si>
@@ -431,9 +488,6 @@
     <t xml:space="preserve">Williams</t>
   </si>
   <si>
-    <t xml:space="preserve">Kavanaugh; Thomas</t>
-  </si>
-  <si>
     <t xml:space="preserve">A.J.T.</t>
   </si>
   <si>
@@ -501,9 +555,6 @@
   </si>
   <si>
     <t xml:space="preserve">2/26/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma</t>
   </si>
   <si>
     <t xml:space="preserve">Rivers</t>
@@ -884,7 +935,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4880.67</v>
+        <v>4727</v>
       </c>
     </row>
     <row r="3">
@@ -892,7 +943,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4811.14</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="4">
@@ -900,7 +951,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>4277.58</v>
+        <v>4917</v>
       </c>
     </row>
     <row r="5">
@@ -908,7 +959,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3094.5</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="6">
@@ -916,7 +967,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3258.38</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +975,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>3786.07</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="8">
@@ -932,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>3416.77</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +991,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>3945.73</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="10">
@@ -948,7 +999,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>3206.7</v>
+        <v>3225</v>
       </c>
     </row>
   </sheetData>
@@ -1042,16 +1093,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>9804</v>
+        <v>12137</v>
       </c>
       <c r="E4" t="s">
         <v>32</v>
@@ -1068,33 +1119,33 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>9368</v>
+        <v>11928</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -1103,19 +1154,19 @@
         <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>8172</v>
+        <v>10702</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
         <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1214,9 +1265,7 @@
       <c r="B4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
+      <c r="C4"/>
       <c r="D4" t="n">
         <v>13</v>
       </c>
@@ -1261,7 +1310,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -1270,7 +1319,7 @@
         <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
@@ -1278,9 +1327,11 @@
       <c r="F6" t="s">
         <v>62</v>
       </c>
-      <c r="G6"/>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
       <c r="H6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1296,19 +1347,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
         <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F1" t="s">
         <v>18</v>
@@ -1316,122 +1367,122 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>34211</v>
+        <v>30456</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>24979</v>
+        <v>25919</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>17728</v>
+        <v>24979</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>17382</v>
+        <v>24020</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>16968</v>
+        <v>22596</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" t="s">
         <v>78</v>
       </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E7" t="n">
+        <v>17728</v>
+      </c>
+      <c r="F7" t="s">
         <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="n">
-        <v>15724</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8">
@@ -1445,13 +1496,13 @@
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>15239</v>
+        <v>17382</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -1468,7 +1519,7 @@
         <v>33</v>
       </c>
       <c r="E9" t="n">
-        <v>14545</v>
+        <v>16781</v>
       </c>
       <c r="F9" t="s">
         <v>35</v>
@@ -1476,142 +1527,142 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>14309</v>
+        <v>15724</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
-        <v>13064</v>
+        <v>15440</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E12" t="n">
-        <v>12658</v>
+        <v>15239</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="E13" t="n">
-        <v>12409</v>
+        <v>15084</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>11838</v>
+        <v>14309</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
-        <v>11345</v>
+        <v>13939</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>11109</v>
+        <v>13664</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -1625,33 +1676,33 @@
         <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
-        <v>10951</v>
+        <v>13607</v>
       </c>
       <c r="F17" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
         <v>103</v>
       </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E18" t="n">
-        <v>10804</v>
+        <v>12924</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -1665,13 +1716,13 @@
         <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
-        <v>10468</v>
+        <v>11945</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
@@ -1679,19 +1730,19 @@
         <v>106</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
         <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>10417</v>
+        <v>11791</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
@@ -1699,139 +1750,139 @@
         <v>108</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
-        <v>10169</v>
+        <v>11345</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="E22" t="n">
-        <v>9856</v>
+        <v>11109</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>9763</v>
+        <v>10951</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="E24" t="n">
-        <v>9694</v>
+        <v>10481</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="E25" t="n">
-        <v>8975</v>
+        <v>10468</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E26" t="n">
-        <v>8767</v>
+        <v>10351</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>8021</v>
+        <v>10169</v>
       </c>
       <c r="F27" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -1839,179 +1890,179 @@
         <v>123</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" t="s">
         <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>7084</v>
+        <v>10048</v>
       </c>
       <c r="F28" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
         <v>126</v>
       </c>
-      <c r="B29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9856</v>
+      </c>
+      <c r="F29" t="s">
         <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" t="n">
-        <v>7036</v>
-      </c>
-      <c r="F29" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
         <v>129</v>
       </c>
-      <c r="B30" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" t="s">
-        <v>130</v>
-      </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="E30" t="n">
-        <v>6988</v>
+        <v>9763</v>
       </c>
       <c r="F30" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E31" t="n">
-        <v>6886</v>
+        <v>9410</v>
       </c>
       <c r="F31" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="E32" t="n">
-        <v>6771</v>
+        <v>8975</v>
       </c>
       <c r="F32" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8767</v>
+      </c>
+      <c r="F33" t="s">
         <v>137</v>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" t="n">
-        <v>6675</v>
-      </c>
-      <c r="F33" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="E34" t="n">
-        <v>6571</v>
+        <v>8308</v>
       </c>
       <c r="F34" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="D35" t="s">
         <v>28</v>
       </c>
       <c r="E35" t="n">
-        <v>6398</v>
+        <v>8021</v>
       </c>
       <c r="F35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
         <v>143</v>
       </c>
-      <c r="B36" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7084</v>
+      </c>
+      <c r="F36" t="s">
         <v>144</v>
-      </c>
-      <c r="D36" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" t="n">
-        <v>6346</v>
-      </c>
-      <c r="F36" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="37">
@@ -2022,273 +2073,273 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
         <v>28</v>
       </c>
       <c r="E37" t="n">
-        <v>6156</v>
+        <v>7036</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E38" t="n">
-        <v>6142</v>
+        <v>6988</v>
       </c>
       <c r="F38" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="E39" t="n">
-        <v>5504</v>
+        <v>6886</v>
       </c>
       <c r="F39" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="D40" t="s">
         <v>28</v>
       </c>
       <c r="E40" t="n">
-        <v>5446</v>
+        <v>6771</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="E41" t="n">
-        <v>5438</v>
+        <v>6675</v>
       </c>
       <c r="F41" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s">
         <v>28</v>
       </c>
       <c r="E42" t="n">
-        <v>5260</v>
+        <v>6571</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="D43" t="s">
         <v>28</v>
       </c>
       <c r="E43" t="n">
-        <v>4756</v>
+        <v>6398</v>
       </c>
       <c r="F43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D44" t="s">
         <v>51</v>
       </c>
       <c r="E44" t="n">
-        <v>4724</v>
+        <v>6346</v>
       </c>
       <c r="F44" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="D45" t="s">
         <v>28</v>
       </c>
       <c r="E45" t="n">
-        <v>4151</v>
+        <v>6156</v>
       </c>
       <c r="F45" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="D46" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E46" t="n">
-        <v>3988</v>
+        <v>6142</v>
       </c>
       <c r="F46" t="s">
-        <v>35</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E47" t="n">
-        <v>3908</v>
+        <v>5504</v>
       </c>
       <c r="F47" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D48" t="s">
         <v>28</v>
       </c>
       <c r="E48" t="n">
-        <v>3835</v>
+        <v>5446</v>
       </c>
       <c r="F48" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="D49" t="s">
         <v>28</v>
       </c>
       <c r="E49" t="n">
-        <v>3748</v>
+        <v>5438</v>
       </c>
       <c r="F49" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
         <v>28</v>
       </c>
       <c r="E50" t="n">
-        <v>3523</v>
+        <v>5260</v>
       </c>
       <c r="F50" t="s">
         <v>53</v>
@@ -2296,161 +2347,321 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="D51" t="s">
         <v>28</v>
       </c>
       <c r="E51" t="n">
-        <v>3401</v>
+        <v>4756</v>
       </c>
       <c r="F51" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E52" t="n">
-        <v>3264</v>
+        <v>4724</v>
       </c>
       <c r="F52" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="D53" t="s">
         <v>28</v>
       </c>
       <c r="E53" t="n">
-        <v>2413</v>
+        <v>4151</v>
       </c>
       <c r="F53" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E54" t="n">
-        <v>1680</v>
+        <v>3908</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>182</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E55" t="n">
-        <v>430</v>
+        <v>3835</v>
       </c>
       <c r="F55" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>183</v>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>3748</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="D57" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E57" t="n">
-        <v>13</v>
+        <v>3564</v>
       </c>
       <c r="F57" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>184</v>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3523</v>
+      </c>
+      <c r="F58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>28</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3401</v>
+      </c>
+      <c r="F59" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>188</v>
+      </c>
+      <c r="D60" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3264</v>
+      </c>
+      <c r="F60" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>101</v>
+      </c>
+      <c r="D61" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2413</v>
+      </c>
+      <c r="F61" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>50</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>190</v>
+      </c>
+      <c r="D62" t="s">
+        <v>51</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1680</v>
+      </c>
+      <c r="F62" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>191</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
         <v>40</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D63" t="s">
         <v>40</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E63" t="n">
+        <v>430</v>
+      </c>
+      <c r="F63" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>40</v>
+      </c>
+      <c r="D64" t="s">
+        <v>56</v>
+      </c>
+      <c r="E64" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" t="n">
         <v>13</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F65" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>40</v>
+      </c>
+      <c r="D66" t="s">
+        <v>40</v>
+      </c>
+      <c r="E66" t="n">
+        <v>13</v>
+      </c>
+      <c r="F66" t="s">
         <v>48</v>
       </c>
     </row>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/opinion_lengths.xlsx
@@ -10,12 +10,13 @@
     <sheet name="longest_opinions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="shortest_opinions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="combined_opinion_lengths" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="all_individual_opinion_lengths" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -110,490 +111,727 @@
     <t xml:space="preserve">4/2/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">24A884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. CASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/15/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/27/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-316</t>
   </si>
   <si>
     <t xml:space="preserve">Kennedy</t>
   </si>
   <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
     <t xml:space="preserve">4/21/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">6/27/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">24-297</t>
   </si>
   <si>
+    <t xml:space="preserve">Mahmoud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/22/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/13/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/11/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/6/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/22/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/29/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/30/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/22/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special Concurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/25/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/18/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_opinions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_authors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Jackson; Kavanaugh; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrmetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Kagan; Roberts; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumers' Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Kagan; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderstok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Gorsuch; Jackson; Kavanaugh; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/26/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Marijuana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Jackson; Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Speech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kousisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Gorsuch; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/26/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Gorsuch; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/20/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guitierrez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hewitt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kavanaugh; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bufkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/5/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delligatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/21/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esteras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett; Jackson; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calumet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McLaughlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF v. EPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perttu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/29/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Per Curiam; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/21/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> R.J. Reynolds </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wisconsin Bell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Kavanaugh; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/21/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Kavanaugh; Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/16/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Per Curiam; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/17/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kavanaugh; Per Curiam; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/7/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.J.T.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts; Sotomayor; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Canin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/15/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOE v. CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kagan; Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/4/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett; Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith and Wesson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson; Kagan; Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cunningham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/17/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOM Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parrish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch; Jackson; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waetzig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/26/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito; Jackson; Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC/Devas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouarfa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/10/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dewberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan; Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.M.D. Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh; Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/4/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-6573</t>
+  </si>
+  <si>
     <t xml:space="preserve">Concurrence</t>
   </si>
   <si>
-    <t xml:space="preserve">Mahmoud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/22/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/13/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/11/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facebook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/6/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/22/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laboratory Corp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/29/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/5/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drummond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4-4)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/30/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/22/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Special Concurrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/25/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/18/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">case_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_opinions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_authors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_words</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skrmetti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett; Kagan; Roberts; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumers' Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Jackson; Kagan; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanderstok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Gorsuch; Jackson; Kavanaugh; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/26/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical Marijuana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Jackson; Kavanaugh; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Speech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kousisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Gorsuch; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Jackson; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/26/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velazquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett; Gorsuch; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stanley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Jackson; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/20/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guitierrez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hewitt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuld</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Kavanaugh; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catholic Charities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bufkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/5/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delligatti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/21/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esteras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett; Jackson; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calumet </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feliciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McLaughlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF v. EPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/4/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lackey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perttu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/29/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Per Curiam; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/21/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> R.J. Reynolds </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisconsin Bell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Kavanaugh; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/21/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.A.R.P v. Trump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Kavanaugh; Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/16/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/12/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TikTok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Per Curiam; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/17/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trump v. J.G.G.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Kavanaugh; Per Curiam; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/7/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.J.T.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts; Sotomayor; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal Canin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/15/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ames</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOE v. CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Kagan; Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/4/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett; Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith and Wesson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson; Kagan; Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cunningham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/17/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOM Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/15/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parrish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch; Jackson; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waetzig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/26/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito; Jackson; Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC/Devas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bouarfa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/10/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dewberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan; Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E.M.D. Sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh; Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/4/2024</t>
+    <t xml:space="preserve">23-1127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/15/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-7809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/24/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/5/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/8/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/14/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/4/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/13/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-7483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/23/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/22/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/12/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/24/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/28/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/9/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/31/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/7/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/16/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/1/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/3/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1122</t>
   </si>
 </sst>
 </file>
@@ -943,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4864</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="4">
@@ -951,7 +1189,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>4917</v>
+        <v>4678</v>
       </c>
     </row>
     <row r="5">
@@ -959,7 +1197,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3614</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="6">
@@ -983,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>3852</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="9">
@@ -991,7 +1229,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>3380</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="10">
@@ -999,7 +1237,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>3225</v>
+        <v>3390</v>
       </c>
     </row>
   </sheetData>
@@ -1093,16 +1331,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>12137</v>
+        <v>13825</v>
       </c>
       <c r="E4" t="s">
         <v>32</v>
@@ -1119,25 +1357,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>36</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12137</v>
+      </c>
+      <c r="E5" t="s">
         <v>37</v>
-      </c>
-      <c r="D5" t="n">
-        <v>11928</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
         <v>35</v>
@@ -1145,25 +1383,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>10702</v>
+        <v>11928</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
         <v>35</v>
@@ -1208,104 +1446,104 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
         <v>42</v>
       </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="n">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -1313,25 +1551,25 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
         <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1347,19 +1585,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
         <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F1" t="s">
         <v>18</v>
@@ -1367,99 +1605,99 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>30456</v>
+        <v>35216</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>25919</v>
+        <v>30456</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
-        <v>24979</v>
+        <v>25919</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>24020</v>
+        <v>24979</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>22596</v>
+        <v>24020</v>
       </c>
       <c r="F6" t="s">
         <v>35</v>
@@ -1467,42 +1705,42 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>17728</v>
+        <v>22596</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
         <v>80</v>
       </c>
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>81</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="n">
+        <v>17728</v>
+      </c>
+      <c r="F8" t="s">
         <v>82</v>
-      </c>
-      <c r="E8" t="n">
-        <v>17382</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -1510,59 +1748,59 @@
         <v>83</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
         <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="E9" t="n">
-        <v>16781</v>
+        <v>17382</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>15724</v>
+        <v>16781</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>15440</v>
+        <v>15724</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -1570,219 +1808,219 @@
         <v>90</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
         <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
-        <v>15239</v>
+        <v>15440</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B13" t="n">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E13" t="n">
-        <v>15084</v>
+        <v>15239</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
         <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="E14" t="n">
-        <v>14309</v>
+        <v>15084</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E15" t="n">
-        <v>13939</v>
+        <v>14309</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
-        <v>13664</v>
+        <v>13939</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="E17" t="n">
-        <v>13607</v>
+        <v>13664</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
-        <v>12924</v>
+        <v>13607</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="E19" t="n">
-        <v>11945</v>
+        <v>12924</v>
       </c>
       <c r="F19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>11791</v>
+        <v>11945</v>
       </c>
       <c r="F20" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
-        <v>11345</v>
+        <v>11791</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>11109</v>
+        <v>11345</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -1796,10 +2034,10 @@
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
-        <v>10951</v>
+        <v>11109</v>
       </c>
       <c r="F23" t="s">
         <v>115</v>
@@ -1810,19 +2048,19 @@
         <v>116</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
         <v>117</v>
       </c>
       <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10951</v>
+      </c>
+      <c r="F24" t="s">
         <v>118</v>
-      </c>
-      <c r="E24" t="n">
-        <v>10481</v>
-      </c>
-      <c r="F24" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -1830,99 +2068,99 @@
         <v>119</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="E25" t="n">
-        <v>10468</v>
+        <v>10481</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
-        <v>10351</v>
+        <v>10468</v>
       </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B27" t="n">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="n">
-        <v>10169</v>
+        <v>10351</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="E28" t="n">
-        <v>10048</v>
+        <v>10169</v>
       </c>
       <c r="F28" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>9856</v>
+        <v>10048</v>
       </c>
       <c r="F29" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
@@ -1936,53 +2174,53 @@
         <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E30" t="n">
-        <v>9763</v>
+        <v>9856</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" t="n">
-        <v>9410</v>
+        <v>9763</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B32" t="n">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E32" t="n">
-        <v>8975</v>
+        <v>9410</v>
       </c>
       <c r="F32" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33">
@@ -1990,16 +2228,16 @@
         <v>135</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" t="s">
         <v>136</v>
       </c>
       <c r="D33" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E33" t="n">
-        <v>8767</v>
+        <v>8975</v>
       </c>
       <c r="F33" t="s">
         <v>137</v>
@@ -2010,39 +2248,39 @@
         <v>138</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E34" t="n">
-        <v>8308</v>
+        <v>8767</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="E35" t="n">
-        <v>8021</v>
+        <v>8308</v>
       </c>
       <c r="F35" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36">
@@ -2056,10 +2294,10 @@
         <v>143</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="E36" t="n">
-        <v>7084</v>
+        <v>8021</v>
       </c>
       <c r="F36" t="s">
         <v>144</v>
@@ -2070,16 +2308,16 @@
         <v>145</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="s">
         <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="E37" t="n">
-        <v>7036</v>
+        <v>7084</v>
       </c>
       <c r="F37" t="s">
         <v>147</v>
@@ -2090,7 +2328,7 @@
         <v>148</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="s">
         <v>149</v>
@@ -2099,7 +2337,7 @@
         <v>28</v>
       </c>
       <c r="E38" t="n">
-        <v>6988</v>
+        <v>7036</v>
       </c>
       <c r="F38" t="s">
         <v>150</v>
@@ -2110,159 +2348,159 @@
         <v>151</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
         <v>152</v>
       </c>
       <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6988</v>
+      </c>
+      <c r="F39" t="s">
         <v>153</v>
-      </c>
-      <c r="E39" t="n">
-        <v>6886</v>
-      </c>
-      <c r="F39" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
         <v>155</v>
       </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>5</v>
-      </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="E40" t="n">
-        <v>6771</v>
+        <v>6886</v>
       </c>
       <c r="F40" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="E41" t="n">
-        <v>6675</v>
+        <v>6771</v>
       </c>
       <c r="F41" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="E42" t="n">
-        <v>6571</v>
+        <v>6675</v>
       </c>
       <c r="F42" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="D43" t="s">
         <v>28</v>
       </c>
       <c r="E43" t="n">
-        <v>6398</v>
+        <v>6571</v>
       </c>
       <c r="F43" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
+        <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E44" t="n">
-        <v>6346</v>
+        <v>6398</v>
       </c>
       <c r="F44" t="s">
-        <v>79</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E45" t="n">
-        <v>6156</v>
+        <v>6346</v>
       </c>
       <c r="F45" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="E46" t="n">
-        <v>6142</v>
+        <v>6156</v>
       </c>
       <c r="F46" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47">
@@ -2270,119 +2508,119 @@
         <v>167</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" t="s">
         <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E47" t="n">
-        <v>5504</v>
+        <v>6142</v>
       </c>
       <c r="F47" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E48" t="n">
-        <v>5446</v>
+        <v>5504</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="D49" t="s">
         <v>28</v>
       </c>
       <c r="E49" t="n">
-        <v>5438</v>
+        <v>5446</v>
       </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B50" t="n">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D50" t="s">
         <v>28</v>
       </c>
       <c r="E50" t="n">
-        <v>5260</v>
+        <v>5438</v>
       </c>
       <c r="F50" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D51" t="s">
         <v>28</v>
       </c>
       <c r="E51" t="n">
-        <v>4756</v>
+        <v>5260</v>
       </c>
       <c r="F51" t="s">
-        <v>175</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E52" t="n">
-        <v>4724</v>
+        <v>4756</v>
       </c>
       <c r="F52" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
@@ -2390,19 +2628,19 @@
         <v>178</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="D53" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E53" t="n">
-        <v>4151</v>
+        <v>4724</v>
       </c>
       <c r="F53" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54">
@@ -2413,36 +2651,36 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D54" t="s">
         <v>28</v>
       </c>
       <c r="E54" t="n">
-        <v>3908</v>
+        <v>4151</v>
       </c>
       <c r="F54" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>182</v>
+        <v>10</v>
       </c>
       <c r="D55" t="s">
         <v>28</v>
       </c>
       <c r="E55" t="n">
-        <v>3835</v>
+        <v>3908</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56">
@@ -2450,79 +2688,79 @@
         <v>183</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
         <v>28</v>
       </c>
       <c r="E56" t="n">
-        <v>3748</v>
+        <v>3835</v>
       </c>
       <c r="F56" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E57" t="n">
-        <v>3564</v>
+        <v>3748</v>
       </c>
       <c r="F57" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="E58" t="n">
-        <v>3523</v>
+        <v>3564</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D59" t="s">
         <v>28</v>
       </c>
       <c r="E59" t="n">
-        <v>3401</v>
+        <v>3523</v>
       </c>
       <c r="F59" t="s">
-        <v>186</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60">
@@ -2530,19 +2768,19 @@
         <v>187</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="D60" t="s">
         <v>28</v>
       </c>
       <c r="E60" t="n">
-        <v>3264</v>
+        <v>3401</v>
       </c>
       <c r="F60" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61">
@@ -2553,116 +2791,4407 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="D61" t="s">
         <v>28</v>
       </c>
       <c r="E61" t="n">
-        <v>2413</v>
+        <v>3264</v>
       </c>
       <c r="F61" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="B62" t="n">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E62" t="n">
-        <v>1680</v>
+        <v>2413</v>
       </c>
       <c r="F62" t="s">
-        <v>53</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="D63" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E63" t="n">
-        <v>430</v>
+        <v>1680</v>
       </c>
       <c r="F63" t="s">
-        <v>192</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D64" t="s">
+        <v>42</v>
+      </c>
+      <c r="E64" t="n">
+        <v>430</v>
+      </c>
+      <c r="F64" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>57</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>42</v>
+      </c>
+      <c r="D65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
+        <v>22</v>
+      </c>
+      <c r="F65" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66" t="s">
+        <v>42</v>
+      </c>
+      <c r="E66" t="n">
+        <v>13</v>
+      </c>
+      <c r="F66" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>42</v>
+      </c>
+      <c r="D67" t="s">
+        <v>42</v>
+      </c>
+      <c r="E67" t="n">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
         <v>56</v>
       </c>
-      <c r="E64" t="n">
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="n">
         <v>22</v>
       </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" t="n">
+        <v>82</v>
+      </c>
+      <c r="E7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7"/>
+      <c r="H7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" t="n">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>194</v>
+      </c>
+      <c r="H8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" t="n">
+        <v>110</v>
+      </c>
+      <c r="E9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="n">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" t="n">
+        <v>195</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>203</v>
+      </c>
+      <c r="H12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" t="n">
+        <v>205</v>
+      </c>
+      <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" t="s">
+        <v>205</v>
+      </c>
+      <c r="H13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" t="n">
+        <v>217</v>
+      </c>
+      <c r="E14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>207</v>
+      </c>
+      <c r="H14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" t="n">
+        <v>219</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" t="n">
+        <v>223</v>
+      </c>
+      <c r="E16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>210</v>
+      </c>
+      <c r="H16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>254</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" t="s">
+        <v>212</v>
+      </c>
+      <c r="H17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>254</v>
+      </c>
+      <c r="E18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" t="n">
+        <v>288</v>
+      </c>
+      <c r="E19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19"/>
+      <c r="H19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="n">
+        <v>290</v>
+      </c>
+      <c r="E20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20"/>
+      <c r="H20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" t="n">
+        <v>333</v>
+      </c>
+      <c r="E21" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21"/>
+      <c r="H21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" t="n">
+        <v>340</v>
+      </c>
+      <c r="E22" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="n">
+        <v>384</v>
+      </c>
+      <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" t="s">
+        <v>219</v>
+      </c>
+      <c r="H23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>408</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24"/>
+      <c r="H24" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" t="n">
+        <v>422</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" t="s">
+        <v>205</v>
+      </c>
+      <c r="H25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="n">
+        <v>430</v>
+      </c>
+      <c r="E26" t="s">
+        <v>193</v>
+      </c>
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26"/>
+      <c r="H26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" t="s">
+        <v>196</v>
+      </c>
+      <c r="D27" t="n">
+        <v>468</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" t="s">
+        <v>205</v>
+      </c>
+      <c r="H27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>221</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="n">
+        <v>479</v>
+      </c>
+      <c r="E28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="n">
+        <v>653</v>
+      </c>
+      <c r="E29" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="n">
+        <v>655</v>
+      </c>
+      <c r="E30" t="s">
+        <v>167</v>
+      </c>
+      <c r="F30" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30"/>
+      <c r="H30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="n">
+        <v>685</v>
+      </c>
+      <c r="E31" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" t="n">
+        <v>697</v>
+      </c>
+      <c r="E32" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" t="s">
+        <v>224</v>
+      </c>
+      <c r="H32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>217</v>
+      </c>
+      <c r="C33" t="s">
+        <v>196</v>
+      </c>
+      <c r="D33" t="n">
+        <v>701</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" t="s">
+        <v>130</v>
+      </c>
+      <c r="H33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="n">
+        <v>754</v>
+      </c>
+      <c r="E34" t="s">
+        <v>178</v>
+      </c>
+      <c r="F34" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>225</v>
+      </c>
+      <c r="C35" t="s">
+        <v>196</v>
+      </c>
+      <c r="D35" t="n">
+        <v>764</v>
+      </c>
+      <c r="E35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" t="s">
+        <v>226</v>
+      </c>
+      <c r="H35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" t="n">
+        <v>857</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>227</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" t="n">
+        <v>864</v>
+      </c>
+      <c r="E37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" t="n">
+        <v>922</v>
+      </c>
+      <c r="E38" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" t="s">
+        <v>46</v>
+      </c>
+      <c r="H38" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" t="n">
+        <v>952</v>
+      </c>
+      <c r="E39" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" t="s">
+        <v>210</v>
+      </c>
+      <c r="H39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" t="s">
+        <v>214</v>
+      </c>
+      <c r="C40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" t="n">
+        <v>994</v>
+      </c>
+      <c r="E40" t="s">
+        <v>154</v>
+      </c>
+      <c r="F40" t="s">
+        <v>156</v>
+      </c>
+      <c r="G40"/>
+      <c r="H40" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>230</v>
+      </c>
+      <c r="C41" t="s">
+        <v>196</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1275</v>
+      </c>
+      <c r="E41" t="s">
+        <v>102</v>
+      </c>
+      <c r="F41" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41" t="s">
+        <v>231</v>
+      </c>
+      <c r="H41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1287</v>
+      </c>
+      <c r="E43" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" t="s">
+        <v>233</v>
+      </c>
+      <c r="H43" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1353</v>
+      </c>
+      <c r="E44" t="s">
+        <v>151</v>
+      </c>
+      <c r="F44" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" t="s">
+        <v>207</v>
+      </c>
+      <c r="H44" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" t="s">
+        <v>196</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1373</v>
+      </c>
+      <c r="E45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F45" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" t="s">
+        <v>233</v>
+      </c>
+      <c r="H45" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1384</v>
+      </c>
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E47" t="s">
+        <v>79</v>
+      </c>
+      <c r="F47" t="s">
+        <v>81</v>
+      </c>
+      <c r="G47" t="s">
+        <v>205</v>
+      </c>
+      <c r="H47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1667</v>
+      </c>
+      <c r="E48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48" t="s">
+        <v>54</v>
+      </c>
+      <c r="H48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>234</v>
+      </c>
+      <c r="C49" t="s">
+        <v>196</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1708</v>
+      </c>
+      <c r="E49" t="s">
+        <v>148</v>
+      </c>
+      <c r="F49" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" t="s">
+        <v>54</v>
+      </c>
+      <c r="H49" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>235</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1766</v>
+      </c>
+      <c r="E50" t="s">
+        <v>176</v>
+      </c>
+      <c r="F50" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" t="s">
+        <v>236</v>
+      </c>
+      <c r="H50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1928</v>
+      </c>
+      <c r="E51" t="s">
+        <v>177</v>
+      </c>
+      <c r="F51" t="s">
+        <v>28</v>
+      </c>
+      <c r="G51" t="s">
+        <v>226</v>
+      </c>
+      <c r="H51" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" t="s">
+        <v>202</v>
+      </c>
+      <c r="C52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2213</v>
+      </c>
+      <c r="E52" t="s">
+        <v>191</v>
+      </c>
+      <c r="F52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" t="s">
+        <v>203</v>
+      </c>
+      <c r="H52" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s">
+        <v>238</v>
+      </c>
+      <c r="C53" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2221</v>
+      </c>
+      <c r="E53" t="s">
+        <v>166</v>
+      </c>
+      <c r="F53" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" t="s">
+        <v>181</v>
+      </c>
+      <c r="H53" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2316</v>
+      </c>
+      <c r="E54" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" t="s">
+        <v>240</v>
+      </c>
+      <c r="H54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" t="s">
+        <v>229</v>
+      </c>
+      <c r="C55" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2342</v>
+      </c>
+      <c r="E55" t="s">
+        <v>189</v>
+      </c>
+      <c r="F55" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" t="s">
+        <v>46</v>
+      </c>
+      <c r="H55" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" t="s">
+        <v>241</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2367</v>
+      </c>
+      <c r="E56" t="s">
+        <v>170</v>
+      </c>
+      <c r="F56" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" t="s">
+        <v>41</v>
+      </c>
+      <c r="H56" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" t="s">
+        <v>216</v>
+      </c>
+      <c r="C57" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E57" t="s">
+        <v>145</v>
+      </c>
+      <c r="F57" t="s">
+        <v>81</v>
+      </c>
+      <c r="G57"/>
+      <c r="H57" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>218</v>
+      </c>
+      <c r="C58" t="s">
+        <v>62</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2575</v>
+      </c>
+      <c r="E58" t="s">
+        <v>95</v>
+      </c>
+      <c r="F58" t="s">
+        <v>97</v>
+      </c>
+      <c r="G58" t="s">
+        <v>219</v>
+      </c>
+      <c r="H58" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2660</v>
+      </c>
+      <c r="E59" t="s">
+        <v>183</v>
+      </c>
+      <c r="F59" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" t="s">
+        <v>210</v>
+      </c>
+      <c r="H59" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>242</v>
+      </c>
+      <c r="C60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2702</v>
+      </c>
+      <c r="E60" t="s">
+        <v>111</v>
+      </c>
+      <c r="F60" t="s">
+        <v>28</v>
+      </c>
+      <c r="G60" t="s">
+        <v>243</v>
+      </c>
+      <c r="H60" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" t="s">
+        <v>211</v>
+      </c>
+      <c r="C61" t="s">
+        <v>196</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2771</v>
+      </c>
+      <c r="E61" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>212</v>
+      </c>
+      <c r="H61" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" t="s">
+        <v>237</v>
+      </c>
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2828</v>
+      </c>
+      <c r="E62" t="s">
+        <v>177</v>
+      </c>
+      <c r="F62" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" t="s">
+        <v>226</v>
+      </c>
+      <c r="H62" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" t="s">
+        <v>244</v>
+      </c>
+      <c r="C63" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2947</v>
+      </c>
+      <c r="E63" t="s">
+        <v>159</v>
+      </c>
+      <c r="F63" t="s">
+        <v>85</v>
+      </c>
+      <c r="G63" t="s">
+        <v>245</v>
+      </c>
+      <c r="H63" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>246</v>
+      </c>
+      <c r="C64" t="s">
+        <v>62</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3005</v>
+      </c>
+      <c r="E64" t="s">
+        <v>135</v>
+      </c>
       <c r="F64" t="s">
-        <v>58</v>
+        <v>64</v>
+      </c>
+      <c r="G64" t="s">
+        <v>188</v>
+      </c>
+      <c r="H64" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
         <v>42</v>
       </c>
-      <c r="B65" t="n">
-        <v>1</v>
+      <c r="B65" t="s">
+        <v>195</v>
       </c>
       <c r="C65" t="s">
-        <v>40</v>
-      </c>
-      <c r="D65" t="s">
-        <v>40</v>
-      </c>
-      <c r="E65" t="n">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3035</v>
+      </c>
+      <c r="E65" t="s">
+        <v>138</v>
       </c>
       <c r="F65" t="s">
-        <v>44</v>
+        <v>81</v>
+      </c>
+      <c r="G65"/>
+      <c r="H65" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="B66" t="s">
+        <v>208</v>
       </c>
       <c r="C66" t="s">
+        <v>196</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3118</v>
+      </c>
+      <c r="E66" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s">
+        <v>82</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>241</v>
+      </c>
+      <c r="C67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3137</v>
+      </c>
+      <c r="E67" t="s">
+        <v>170</v>
+      </c>
+      <c r="F67" t="s">
+        <v>53</v>
+      </c>
+      <c r="G67" t="s">
+        <v>41</v>
+      </c>
+      <c r="H67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>247</v>
+      </c>
+      <c r="C68" t="s">
+        <v>196</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3198</v>
+      </c>
+      <c r="E68" t="s">
+        <v>90</v>
+      </c>
+      <c r="F68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" t="s">
+        <v>30</v>
+      </c>
+      <c r="H68" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" t="s">
+        <v>248</v>
+      </c>
+      <c r="C69" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3224</v>
+      </c>
+      <c r="E69" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" t="s">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H69" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3239</v>
+      </c>
+      <c r="E70" t="s">
+        <v>93</v>
+      </c>
+      <c r="F70" t="s">
+        <v>85</v>
+      </c>
+      <c r="G70" t="s">
+        <v>228</v>
+      </c>
+      <c r="H70" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3289</v>
+      </c>
+      <c r="E71" t="s">
         <v>40</v>
       </c>
-      <c r="D66" t="s">
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71" t="s">
+        <v>41</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" t="s">
+        <v>198</v>
+      </c>
+      <c r="C72" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3325</v>
+      </c>
+      <c r="E72" t="s">
+        <v>83</v>
+      </c>
+      <c r="F72" t="s">
+        <v>85</v>
+      </c>
+      <c r="G72" t="s">
+        <v>199</v>
+      </c>
+      <c r="H72" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B73" t="s">
+        <v>249</v>
+      </c>
+      <c r="C73" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3401</v>
+      </c>
+      <c r="E73" t="s">
+        <v>187</v>
+      </c>
+      <c r="F73" t="s">
+        <v>28</v>
+      </c>
+      <c r="G73" t="s">
+        <v>199</v>
+      </c>
+      <c r="H73" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" t="s">
+        <v>239</v>
+      </c>
+      <c r="C74" t="s">
+        <v>196</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3420</v>
+      </c>
+      <c r="E74" t="s">
+        <v>88</v>
+      </c>
+      <c r="F74" t="s">
+        <v>28</v>
+      </c>
+      <c r="G74" t="s">
+        <v>240</v>
+      </c>
+      <c r="H74" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" t="s">
+        <v>196</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3460</v>
+      </c>
+      <c r="E75" t="s">
+        <v>32</v>
+      </c>
+      <c r="F75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G75" t="s">
+        <v>34</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" t="s">
+        <v>61</v>
+      </c>
+      <c r="C76" t="s">
+        <v>26</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3483</v>
+      </c>
+      <c r="E76" t="s">
+        <v>63</v>
+      </c>
+      <c r="F76" t="s">
+        <v>64</v>
+      </c>
+      <c r="G76" t="s">
+        <v>65</v>
+      </c>
+      <c r="H76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" t="s">
+        <v>235</v>
+      </c>
+      <c r="C77" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3494</v>
+      </c>
+      <c r="E77" t="s">
+        <v>176</v>
+      </c>
+      <c r="F77" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" t="s">
+        <v>236</v>
+      </c>
+      <c r="H77" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>250</v>
+      </c>
+      <c r="C78" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3523</v>
+      </c>
+      <c r="E78" t="s">
+        <v>186</v>
+      </c>
+      <c r="F78" t="s">
+        <v>28</v>
+      </c>
+      <c r="G78" t="s">
+        <v>236</v>
+      </c>
+      <c r="H78" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" t="s">
+        <v>197</v>
+      </c>
+      <c r="C79" t="s">
+        <v>196</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3640</v>
+      </c>
+      <c r="E79" t="s">
+        <v>142</v>
+      </c>
+      <c r="F79" t="s">
+        <v>28</v>
+      </c>
+      <c r="G79" t="s">
+        <v>194</v>
+      </c>
+      <c r="H79" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>213</v>
+      </c>
+      <c r="C80" t="s">
+        <v>26</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3716</v>
+      </c>
+      <c r="E80" t="s">
+        <v>178</v>
+      </c>
+      <c r="F80" t="s">
+        <v>53</v>
+      </c>
+      <c r="G80" t="s">
+        <v>38</v>
+      </c>
+      <c r="H80" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" t="s">
+        <v>244</v>
+      </c>
+      <c r="C81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3728</v>
+      </c>
+      <c r="E81" t="s">
+        <v>159</v>
+      </c>
+      <c r="F81" t="s">
+        <v>85</v>
+      </c>
+      <c r="G81" t="s">
+        <v>245</v>
+      </c>
+      <c r="H81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3748</v>
+      </c>
+      <c r="E82" t="s">
+        <v>185</v>
+      </c>
+      <c r="F82" t="s">
+        <v>28</v>
+      </c>
+      <c r="G82" t="s">
+        <v>233</v>
+      </c>
+      <c r="H82" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>200</v>
+      </c>
+      <c r="C83" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3806</v>
+      </c>
+      <c r="E83" t="s">
+        <v>100</v>
+      </c>
+      <c r="F83" t="s">
+        <v>33</v>
+      </c>
+      <c r="G83" t="s">
+        <v>201</v>
+      </c>
+      <c r="H83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" t="s">
+        <v>62</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3817</v>
+      </c>
+      <c r="E84" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" t="s">
+        <v>28</v>
+      </c>
+      <c r="G84" t="s">
+        <v>240</v>
+      </c>
+      <c r="H84" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
+        <v>252</v>
+      </c>
+      <c r="C85" t="s">
+        <v>26</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3908</v>
+      </c>
+      <c r="E85" t="s">
+        <v>182</v>
+      </c>
+      <c r="F85" t="s">
+        <v>28</v>
+      </c>
+      <c r="G85" t="s">
+        <v>243</v>
+      </c>
+      <c r="H85" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>232</v>
+      </c>
+      <c r="C86" t="s">
+        <v>26</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E86" t="s">
+        <v>160</v>
+      </c>
+      <c r="F86" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" t="s">
+        <v>233</v>
+      </c>
+      <c r="H86" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" t="s">
+        <v>238</v>
+      </c>
+      <c r="C87" t="s">
+        <v>196</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3935</v>
+      </c>
+      <c r="E87" t="s">
+        <v>166</v>
+      </c>
+      <c r="F87" t="s">
+        <v>28</v>
+      </c>
+      <c r="G87" t="s">
+        <v>181</v>
+      </c>
+      <c r="H87" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" t="s">
+        <v>253</v>
+      </c>
+      <c r="C88" t="s">
+        <v>20</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3941</v>
+      </c>
+      <c r="E88" t="s">
+        <v>128</v>
+      </c>
+      <c r="F88" t="s">
+        <v>85</v>
+      </c>
+      <c r="G88" t="s">
+        <v>254</v>
+      </c>
+      <c r="H88" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>2</v>
+      </c>
+      <c r="B89" t="s">
+        <v>255</v>
+      </c>
+      <c r="C89" t="s">
+        <v>26</v>
+      </c>
+      <c r="D89" t="n">
+        <v>4050</v>
+      </c>
+      <c r="E89" t="s">
+        <v>131</v>
+      </c>
+      <c r="F89" t="s">
+        <v>81</v>
+      </c>
+      <c r="G89" t="s">
+        <v>205</v>
+      </c>
+      <c r="H89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" t="s">
+        <v>242</v>
+      </c>
+      <c r="C90" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" t="n">
+        <v>4102</v>
+      </c>
+      <c r="E90" t="s">
+        <v>111</v>
+      </c>
+      <c r="F90" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" t="s">
+        <v>243</v>
+      </c>
+      <c r="H90" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>256</v>
+      </c>
+      <c r="C91" t="s">
+        <v>26</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4151</v>
+      </c>
+      <c r="E91" t="s">
+        <v>180</v>
+      </c>
+      <c r="F91" t="s">
+        <v>28</v>
+      </c>
+      <c r="G91" t="s">
+        <v>210</v>
+      </c>
+      <c r="H91" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" t="s">
+        <v>197</v>
+      </c>
+      <c r="C92" t="s">
+        <v>26</v>
+      </c>
+      <c r="D92" t="n">
+        <v>4283</v>
+      </c>
+      <c r="E92" t="s">
+        <v>142</v>
+      </c>
+      <c r="F92" t="s">
+        <v>28</v>
+      </c>
+      <c r="G92" t="s">
+        <v>194</v>
+      </c>
+      <c r="H92" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" t="s">
+        <v>221</v>
+      </c>
+      <c r="C93" t="s">
+        <v>26</v>
+      </c>
+      <c r="D93" t="n">
+        <v>4349</v>
+      </c>
+      <c r="E93" t="s">
+        <v>119</v>
+      </c>
+      <c r="F93" t="s">
+        <v>121</v>
+      </c>
+      <c r="G93" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" t="s">
+        <v>216</v>
+      </c>
+      <c r="C94" t="s">
+        <v>20</v>
+      </c>
+      <c r="D94" t="n">
+        <v>4355</v>
+      </c>
+      <c r="E94" t="s">
+        <v>145</v>
+      </c>
+      <c r="F94" t="s">
+        <v>81</v>
+      </c>
+      <c r="G94"/>
+      <c r="H94" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95" t="s">
+        <v>257</v>
+      </c>
+      <c r="C95" t="s">
+        <v>20</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4367</v>
+      </c>
+      <c r="E95" t="s">
+        <v>126</v>
+      </c>
+      <c r="F95" t="s">
+        <v>33</v>
+      </c>
+      <c r="G95" t="s">
+        <v>140</v>
+      </c>
+      <c r="H95" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" t="s">
+        <v>258</v>
+      </c>
+      <c r="C96" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E96" t="s">
+        <v>124</v>
+      </c>
+      <c r="F96" t="s">
+        <v>81</v>
+      </c>
+      <c r="G96" t="s">
+        <v>65</v>
+      </c>
+      <c r="H96" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" t="s">
+        <v>217</v>
+      </c>
+      <c r="C97" t="s">
+        <v>26</v>
+      </c>
+      <c r="D97" t="n">
+        <v>4405</v>
+      </c>
+      <c r="E97" t="s">
+        <v>172</v>
+      </c>
+      <c r="F97" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" t="s">
+        <v>130</v>
+      </c>
+      <c r="H97" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" t="s">
+        <v>242</v>
+      </c>
+      <c r="C98" t="s">
+        <v>196</v>
+      </c>
+      <c r="D98" t="n">
+        <v>4541</v>
+      </c>
+      <c r="E98" t="s">
+        <v>111</v>
+      </c>
+      <c r="F98" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" t="s">
+        <v>243</v>
+      </c>
+      <c r="H98" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" t="s">
+        <v>259</v>
+      </c>
+      <c r="C99" t="s">
+        <v>26</v>
+      </c>
+      <c r="D99" t="n">
+        <v>4632</v>
+      </c>
+      <c r="E99" t="s">
+        <v>116</v>
+      </c>
+      <c r="F99" t="s">
+        <v>81</v>
+      </c>
+      <c r="G99" t="s">
+        <v>228</v>
+      </c>
+      <c r="H99" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>225</v>
+      </c>
+      <c r="C100" t="s">
+        <v>26</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4674</v>
+      </c>
+      <c r="E100" t="s">
+        <v>174</v>
+      </c>
+      <c r="F100" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" t="s">
+        <v>226</v>
+      </c>
+      <c r="H100" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" t="s">
+        <v>260</v>
+      </c>
+      <c r="C101" t="s">
+        <v>26</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4697</v>
+      </c>
+      <c r="E101" t="s">
+        <v>133</v>
+      </c>
+      <c r="F101" t="s">
+        <v>85</v>
+      </c>
+      <c r="G101" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" t="s">
+        <v>260</v>
+      </c>
+      <c r="C102" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4713</v>
+      </c>
+      <c r="E102" t="s">
+        <v>133</v>
+      </c>
+      <c r="F102" t="s">
+        <v>85</v>
+      </c>
+      <c r="G102" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" t="s">
+        <v>200</v>
+      </c>
+      <c r="C103" t="s">
+        <v>20</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E103" t="s">
+        <v>100</v>
+      </c>
+      <c r="F103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" t="s">
+        <v>201</v>
+      </c>
+      <c r="H103" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>9</v>
+      </c>
+      <c r="B104" t="s">
+        <v>261</v>
+      </c>
+      <c r="C104" t="s">
+        <v>26</v>
+      </c>
+      <c r="D104" t="n">
+        <v>4874</v>
+      </c>
+      <c r="E104" t="s">
+        <v>122</v>
+      </c>
+      <c r="F104" t="s">
+        <v>81</v>
+      </c>
+      <c r="G104" t="s">
+        <v>203</v>
+      </c>
+      <c r="H104" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>10</v>
+      </c>
+      <c r="B105" t="s">
+        <v>223</v>
+      </c>
+      <c r="C105" t="s">
+        <v>20</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4891</v>
+      </c>
+      <c r="E105" t="s">
+        <v>109</v>
+      </c>
+      <c r="F105" t="s">
+        <v>81</v>
+      </c>
+      <c r="G105" t="s">
+        <v>224</v>
+      </c>
+      <c r="H105" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>7</v>
+      </c>
+      <c r="B106" t="s">
+        <v>262</v>
+      </c>
+      <c r="C106" t="s">
+        <v>26</v>
+      </c>
+      <c r="D106" t="n">
+        <v>4912</v>
+      </c>
+      <c r="E106" t="s">
+        <v>125</v>
+      </c>
+      <c r="F106" t="s">
+        <v>85</v>
+      </c>
+      <c r="G106" t="s">
+        <v>240</v>
+      </c>
+      <c r="H106" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>221</v>
+      </c>
+      <c r="C107" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4968</v>
+      </c>
+      <c r="E107" t="s">
+        <v>119</v>
+      </c>
+      <c r="F107" t="s">
+        <v>121</v>
+      </c>
+      <c r="G107" t="s">
+        <v>24</v>
+      </c>
+      <c r="H107" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>4</v>
+      </c>
+      <c r="B108" t="s">
+        <v>230</v>
+      </c>
+      <c r="C108" t="s">
+        <v>26</v>
+      </c>
+      <c r="D108" t="n">
+        <v>4973</v>
+      </c>
+      <c r="E108" t="s">
+        <v>102</v>
+      </c>
+      <c r="F108" t="s">
+        <v>85</v>
+      </c>
+      <c r="G108" t="s">
+        <v>231</v>
+      </c>
+      <c r="H108" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" t="s">
+        <v>263</v>
+      </c>
+      <c r="C109" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109" t="n">
+        <v>4989</v>
+      </c>
+      <c r="E109" t="s">
+        <v>113</v>
+      </c>
+      <c r="F109" t="s">
+        <v>81</v>
+      </c>
+      <c r="G109" t="s">
+        <v>254</v>
+      </c>
+      <c r="H109" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>10</v>
+      </c>
+      <c r="B110" t="s">
+        <v>248</v>
+      </c>
+      <c r="C110" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" t="n">
+        <v>5084</v>
+      </c>
+      <c r="E110" t="s">
+        <v>141</v>
+      </c>
+      <c r="F110" t="s">
+        <v>81</v>
+      </c>
+      <c r="G110" t="s">
+        <v>140</v>
+      </c>
+      <c r="H110" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>4</v>
+      </c>
+      <c r="B111" t="s">
+        <v>200</v>
+      </c>
+      <c r="C111" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" t="n">
+        <v>5192</v>
+      </c>
+      <c r="E111" t="s">
+        <v>100</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111" t="s">
+        <v>201</v>
+      </c>
+      <c r="H111" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>214</v>
+      </c>
+      <c r="C112" t="s">
+        <v>20</v>
+      </c>
+      <c r="D112" t="n">
+        <v>5196</v>
+      </c>
+      <c r="E112" t="s">
+        <v>154</v>
+      </c>
+      <c r="F112" t="s">
+        <v>156</v>
+      </c>
+      <c r="G112"/>
+      <c r="H112" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>10</v>
+      </c>
+      <c r="B113" t="s">
+        <v>215</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" t="n">
+        <v>5197</v>
+      </c>
+      <c r="E113" t="s">
+        <v>167</v>
+      </c>
+      <c r="F113" t="s">
+        <v>85</v>
+      </c>
+      <c r="G113"/>
+      <c r="H113" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" t="s">
+        <v>262</v>
+      </c>
+      <c r="C114" t="s">
+        <v>20</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5257</v>
+      </c>
+      <c r="E114" t="s">
+        <v>125</v>
+      </c>
+      <c r="F114" t="s">
+        <v>85</v>
+      </c>
+      <c r="G114" t="s">
+        <v>240</v>
+      </c>
+      <c r="H114" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" t="s">
+        <v>218</v>
+      </c>
+      <c r="C115" t="s">
+        <v>26</v>
+      </c>
+      <c r="D115" t="n">
+        <v>5265</v>
+      </c>
+      <c r="E115" t="s">
+        <v>95</v>
+      </c>
+      <c r="F115" t="s">
+        <v>97</v>
+      </c>
+      <c r="G115" t="s">
+        <v>219</v>
+      </c>
+      <c r="H115" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B116" t="s">
+        <v>234</v>
+      </c>
+      <c r="C116" t="s">
+        <v>26</v>
+      </c>
+      <c r="D116" t="n">
+        <v>5328</v>
+      </c>
+      <c r="E116" t="s">
+        <v>148</v>
+      </c>
+      <c r="F116" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" t="s">
+        <v>54</v>
+      </c>
+      <c r="H116" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>42</v>
+      </c>
+      <c r="B117" t="s">
+        <v>206</v>
+      </c>
+      <c r="C117" t="s">
+        <v>42</v>
+      </c>
+      <c r="D117" t="n">
+        <v>5418</v>
+      </c>
+      <c r="E117" t="s">
+        <v>151</v>
+      </c>
+      <c r="F117" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" t="s">
+        <v>207</v>
+      </c>
+      <c r="H117" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" t="s">
+        <v>227</v>
+      </c>
+      <c r="C118" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5461</v>
+      </c>
+      <c r="E118" t="s">
+        <v>93</v>
+      </c>
+      <c r="F118" t="s">
+        <v>85</v>
+      </c>
+      <c r="G118" t="s">
+        <v>228</v>
+      </c>
+      <c r="H118" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>10</v>
+      </c>
+      <c r="B119" t="s">
+        <v>261</v>
+      </c>
+      <c r="C119" t="s">
+        <v>20</v>
+      </c>
+      <c r="D119" t="n">
+        <v>5594</v>
+      </c>
+      <c r="E119" t="s">
+        <v>122</v>
+      </c>
+      <c r="F119" t="s">
+        <v>81</v>
+      </c>
+      <c r="G119" t="s">
+        <v>203</v>
+      </c>
+      <c r="H119" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" t="s">
+        <v>195</v>
+      </c>
+      <c r="C120" t="s">
+        <v>20</v>
+      </c>
+      <c r="D120" t="n">
+        <v>5650</v>
+      </c>
+      <c r="E120" t="s">
+        <v>138</v>
+      </c>
+      <c r="F120" t="s">
+        <v>81</v>
+      </c>
+      <c r="G120"/>
+      <c r="H120" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>7</v>
+      </c>
+      <c r="B121" t="s">
+        <v>227</v>
+      </c>
+      <c r="C121" t="s">
+        <v>26</v>
+      </c>
+      <c r="D121" t="n">
+        <v>5675</v>
+      </c>
+      <c r="E121" t="s">
+        <v>93</v>
+      </c>
+      <c r="F121" t="s">
+        <v>85</v>
+      </c>
+      <c r="G121" t="s">
+        <v>228</v>
+      </c>
+      <c r="H121" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" t="s">
+        <v>257</v>
+      </c>
+      <c r="C122" t="s">
+        <v>26</v>
+      </c>
+      <c r="D122" t="n">
+        <v>5681</v>
+      </c>
+      <c r="E122" t="s">
+        <v>126</v>
+      </c>
+      <c r="F122" t="s">
+        <v>33</v>
+      </c>
+      <c r="G122" t="s">
+        <v>140</v>
+      </c>
+      <c r="H122" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>10</v>
+      </c>
+      <c r="B123" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" t="s">
+        <v>26</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5693</v>
+      </c>
+      <c r="E123" t="s">
+        <v>164</v>
+      </c>
+      <c r="F123" t="s">
+        <v>53</v>
+      </c>
+      <c r="G123" t="s">
+        <v>29</v>
+      </c>
+      <c r="H123" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>10</v>
+      </c>
+      <c r="B124" t="s">
+        <v>255</v>
+      </c>
+      <c r="C124" t="s">
+        <v>20</v>
+      </c>
+      <c r="D124" t="n">
+        <v>5713</v>
+      </c>
+      <c r="E124" t="s">
+        <v>131</v>
+      </c>
+      <c r="F124" t="s">
+        <v>81</v>
+      </c>
+      <c r="G124" t="s">
+        <v>205</v>
+      </c>
+      <c r="H124" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>10</v>
+      </c>
+      <c r="B125" t="s">
+        <v>247</v>
+      </c>
+      <c r="C125" t="s">
+        <v>20</v>
+      </c>
+      <c r="D125" t="n">
+        <v>5761</v>
+      </c>
+      <c r="E125" t="s">
+        <v>90</v>
+      </c>
+      <c r="F125" t="s">
+        <v>33</v>
+      </c>
+      <c r="G125" t="s">
+        <v>30</v>
+      </c>
+      <c r="H125" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126" t="s">
+        <v>198</v>
+      </c>
+      <c r="C126" t="s">
+        <v>26</v>
+      </c>
+      <c r="D126" t="n">
+        <v>5775</v>
+      </c>
+      <c r="E126" t="s">
+        <v>83</v>
+      </c>
+      <c r="F126" t="s">
+        <v>85</v>
+      </c>
+      <c r="G126" t="s">
+        <v>199</v>
+      </c>
+      <c r="H126" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>3</v>
+      </c>
+      <c r="B127" t="s">
+        <v>211</v>
+      </c>
+      <c r="C127" t="s">
+        <v>196</v>
+      </c>
+      <c r="D127" t="n">
+        <v>5861</v>
+      </c>
+      <c r="E127" t="s">
+        <v>72</v>
+      </c>
+      <c r="F127" t="s">
+        <v>33</v>
+      </c>
+      <c r="G127" t="s">
+        <v>212</v>
+      </c>
+      <c r="H127" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>4</v>
+      </c>
+      <c r="B128" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" t="s">
+        <v>26</v>
+      </c>
+      <c r="D128" t="n">
+        <v>5915</v>
+      </c>
+      <c r="E128" t="s">
+        <v>128</v>
+      </c>
+      <c r="F128" t="s">
+        <v>85</v>
+      </c>
+      <c r="G128" t="s">
+        <v>254</v>
+      </c>
+      <c r="H128" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>3</v>
+      </c>
+      <c r="B129" t="s">
+        <v>264</v>
+      </c>
+      <c r="C129" t="s">
+        <v>62</v>
+      </c>
+      <c r="D129" t="n">
+        <v>5966</v>
+      </c>
+      <c r="E129" t="s">
+        <v>107</v>
+      </c>
+      <c r="F129" t="s">
+        <v>28</v>
+      </c>
+      <c r="G129" t="s">
+        <v>265</v>
+      </c>
+      <c r="H129" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>3</v>
+      </c>
+      <c r="B130" t="s">
+        <v>258</v>
+      </c>
+      <c r="C130" t="s">
+        <v>26</v>
+      </c>
+      <c r="D130" t="n">
+        <v>5967</v>
+      </c>
+      <c r="E130" t="s">
+        <v>124</v>
+      </c>
+      <c r="F130" t="s">
+        <v>81</v>
+      </c>
+      <c r="G130" t="s">
+        <v>65</v>
+      </c>
+      <c r="H130" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131" t="s">
+        <v>246</v>
+      </c>
+      <c r="C131" t="s">
+        <v>26</v>
+      </c>
+      <c r="D131" t="n">
+        <v>5970</v>
+      </c>
+      <c r="E131" t="s">
+        <v>135</v>
+      </c>
+      <c r="F131" t="s">
+        <v>64</v>
+      </c>
+      <c r="G131" t="s">
+        <v>188</v>
+      </c>
+      <c r="H131" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>2</v>
+      </c>
+      <c r="B132" t="s">
+        <v>264</v>
+      </c>
+      <c r="C132" t="s">
+        <v>26</v>
+      </c>
+      <c r="D132" t="n">
+        <v>5979</v>
+      </c>
+      <c r="E132" t="s">
+        <v>107</v>
+      </c>
+      <c r="F132" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132" t="s">
+        <v>265</v>
+      </c>
+      <c r="H132" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>10</v>
+      </c>
+      <c r="B133" t="s">
+        <v>263</v>
+      </c>
+      <c r="C133" t="s">
+        <v>20</v>
+      </c>
+      <c r="D133" t="n">
+        <v>6120</v>
+      </c>
+      <c r="E133" t="s">
+        <v>113</v>
+      </c>
+      <c r="F133" t="s">
+        <v>81</v>
+      </c>
+      <c r="G133" t="s">
+        <v>254</v>
+      </c>
+      <c r="H133" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>10</v>
+      </c>
+      <c r="B134" t="s">
+        <v>266</v>
+      </c>
+      <c r="C134" t="s">
+        <v>26</v>
+      </c>
+      <c r="D134" t="n">
+        <v>6154</v>
+      </c>
+      <c r="E134" t="s">
+        <v>105</v>
+      </c>
+      <c r="F134" t="s">
+        <v>85</v>
+      </c>
+      <c r="G134" t="s">
+        <v>219</v>
+      </c>
+      <c r="H134" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135" t="s">
+        <v>239</v>
+      </c>
+      <c r="C135" t="s">
+        <v>26</v>
+      </c>
+      <c r="D135" t="n">
+        <v>6171</v>
+      </c>
+      <c r="E135" t="s">
+        <v>88</v>
+      </c>
+      <c r="F135" t="s">
+        <v>28</v>
+      </c>
+      <c r="G135" t="s">
+        <v>240</v>
+      </c>
+      <c r="H135" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" t="s">
+        <v>223</v>
+      </c>
+      <c r="C136" t="s">
+        <v>26</v>
+      </c>
+      <c r="D136" t="n">
+        <v>6203</v>
+      </c>
+      <c r="E136" t="s">
+        <v>109</v>
+      </c>
+      <c r="F136" t="s">
+        <v>81</v>
+      </c>
+      <c r="G136" t="s">
+        <v>224</v>
+      </c>
+      <c r="H136" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>4</v>
+      </c>
+      <c r="B137" t="s">
+        <v>211</v>
+      </c>
+      <c r="C137" t="s">
+        <v>62</v>
+      </c>
+      <c r="D137" t="n">
+        <v>6248</v>
+      </c>
+      <c r="E137" t="s">
+        <v>72</v>
+      </c>
+      <c r="F137" t="s">
+        <v>33</v>
+      </c>
+      <c r="G137" t="s">
+        <v>212</v>
+      </c>
+      <c r="H137" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" t="s">
+        <v>259</v>
+      </c>
+      <c r="C138" t="s">
+        <v>20</v>
+      </c>
+      <c r="D138" t="n">
+        <v>6319</v>
+      </c>
+      <c r="E138" t="s">
+        <v>116</v>
+      </c>
+      <c r="F138" t="s">
+        <v>81</v>
+      </c>
+      <c r="G138" t="s">
+        <v>228</v>
+      </c>
+      <c r="H138" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>6</v>
+      </c>
+      <c r="B139" t="s">
+        <v>267</v>
+      </c>
+      <c r="C139" t="s">
+        <v>26</v>
+      </c>
+      <c r="D139" t="n">
+        <v>6398</v>
+      </c>
+      <c r="E139" t="s">
+        <v>162</v>
+      </c>
+      <c r="F139" t="s">
+        <v>28</v>
+      </c>
+      <c r="G139" t="s">
+        <v>245</v>
+      </c>
+      <c r="H139" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>7</v>
+      </c>
+      <c r="B140" t="s">
+        <v>247</v>
+      </c>
+      <c r="C140" t="s">
+        <v>26</v>
+      </c>
+      <c r="D140" t="n">
+        <v>6481</v>
+      </c>
+      <c r="E140" t="s">
+        <v>90</v>
+      </c>
+      <c r="F140" t="s">
+        <v>33</v>
+      </c>
+      <c r="G140" t="s">
+        <v>30</v>
+      </c>
+      <c r="H140" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" t="s">
+        <v>268</v>
+      </c>
+      <c r="C141" t="s">
+        <v>26</v>
+      </c>
+      <c r="D141" t="n">
+        <v>6601</v>
+      </c>
+      <c r="E141" t="s">
+        <v>103</v>
+      </c>
+      <c r="F141" t="s">
+        <v>33</v>
+      </c>
+      <c r="G141" t="s">
+        <v>115</v>
+      </c>
+      <c r="H141" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>4</v>
+      </c>
+      <c r="B142" t="s">
+        <v>266</v>
+      </c>
+      <c r="C142" t="s">
+        <v>20</v>
+      </c>
+      <c r="D142" t="n">
+        <v>6770</v>
+      </c>
+      <c r="E142" t="s">
+        <v>105</v>
+      </c>
+      <c r="F142" t="s">
+        <v>85</v>
+      </c>
+      <c r="G142" t="s">
+        <v>219</v>
+      </c>
+      <c r="H142" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>5</v>
+      </c>
+      <c r="B143" t="s">
+        <v>269</v>
+      </c>
+      <c r="C143" t="s">
+        <v>26</v>
+      </c>
+      <c r="D143" t="n">
+        <v>6771</v>
+      </c>
+      <c r="E143" t="s">
+        <v>158</v>
+      </c>
+      <c r="F143" t="s">
+        <v>28</v>
+      </c>
+      <c r="G143" t="s">
+        <v>270</v>
+      </c>
+      <c r="H143" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>10</v>
+      </c>
+      <c r="B144" t="s">
+        <v>218</v>
+      </c>
+      <c r="C144" t="s">
+        <v>20</v>
+      </c>
+      <c r="D144" t="n">
+        <v>6860</v>
+      </c>
+      <c r="E144" t="s">
+        <v>95</v>
+      </c>
+      <c r="F144" t="s">
+        <v>97</v>
+      </c>
+      <c r="G144" t="s">
+        <v>219</v>
+      </c>
+      <c r="H144" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>7</v>
+      </c>
+      <c r="B145" t="s">
+        <v>268</v>
+      </c>
+      <c r="C145" t="s">
+        <v>20</v>
+      </c>
+      <c r="D145" t="n">
+        <v>7006</v>
+      </c>
+      <c r="E145" t="s">
+        <v>103</v>
+      </c>
+      <c r="F145" t="s">
+        <v>33</v>
+      </c>
+      <c r="G145" t="s">
+        <v>115</v>
+      </c>
+      <c r="H145" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>2</v>
+      </c>
+      <c r="B146" t="s">
+        <v>211</v>
+      </c>
+      <c r="C146" t="s">
+        <v>26</v>
+      </c>
+      <c r="D146" t="n">
+        <v>7063</v>
+      </c>
+      <c r="E146" t="s">
+        <v>72</v>
+      </c>
+      <c r="F146" t="s">
+        <v>33</v>
+      </c>
+      <c r="G146" t="s">
+        <v>212</v>
+      </c>
+      <c r="H146" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>6</v>
+      </c>
+      <c r="B147" t="s">
+        <v>271</v>
+      </c>
+      <c r="C147" t="s">
+        <v>20</v>
+      </c>
+      <c r="D147" t="n">
+        <v>7141</v>
+      </c>
+      <c r="E147" t="s">
+        <v>86</v>
+      </c>
+      <c r="F147" t="s">
+        <v>33</v>
+      </c>
+      <c r="G147" t="s">
+        <v>163</v>
+      </c>
+      <c r="H147" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>10</v>
+      </c>
+      <c r="B148" t="s">
+        <v>31</v>
+      </c>
+      <c r="C148" t="s">
+        <v>20</v>
+      </c>
+      <c r="D148" t="n">
+        <v>7198</v>
+      </c>
+      <c r="E148" t="s">
+        <v>32</v>
+      </c>
+      <c r="F148" t="s">
+        <v>33</v>
+      </c>
+      <c r="G148" t="s">
+        <v>34</v>
+      </c>
+      <c r="H148" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>7</v>
+      </c>
+      <c r="B149" t="s">
+        <v>204</v>
+      </c>
+      <c r="C149" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" t="n">
+        <v>7223</v>
+      </c>
+      <c r="E149" t="s">
+        <v>79</v>
+      </c>
+      <c r="F149" t="s">
+        <v>81</v>
+      </c>
+      <c r="G149" t="s">
+        <v>205</v>
+      </c>
+      <c r="H149" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>5</v>
+      </c>
+      <c r="B150" t="s">
+        <v>230</v>
+      </c>
+      <c r="C150" t="s">
+        <v>20</v>
+      </c>
+      <c r="D150" t="n">
+        <v>7416</v>
+      </c>
+      <c r="E150" t="s">
+        <v>102</v>
+      </c>
+      <c r="F150" t="s">
+        <v>85</v>
+      </c>
+      <c r="G150" t="s">
+        <v>231</v>
+      </c>
+      <c r="H150" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>3</v>
+      </c>
+      <c r="B151" t="s">
+        <v>204</v>
+      </c>
+      <c r="C151" t="s">
+        <v>20</v>
+      </c>
+      <c r="D151" t="n">
+        <v>7915</v>
+      </c>
+      <c r="E151" t="s">
+        <v>79</v>
+      </c>
+      <c r="F151" t="s">
+        <v>81</v>
+      </c>
+      <c r="G151" t="s">
+        <v>205</v>
+      </c>
+      <c r="H151" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" t="s">
+        <v>198</v>
+      </c>
+      <c r="C152" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" t="n">
+        <v>8172</v>
+      </c>
+      <c r="E152" t="s">
+        <v>83</v>
+      </c>
+      <c r="F152" t="s">
+        <v>85</v>
+      </c>
+      <c r="G152" t="s">
+        <v>199</v>
+      </c>
+      <c r="H152" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>5</v>
+      </c>
+      <c r="B153" t="s">
+        <v>211</v>
+      </c>
+      <c r="C153" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" t="n">
+        <v>8259</v>
+      </c>
+      <c r="E153" t="s">
+        <v>72</v>
+      </c>
+      <c r="F153" t="s">
+        <v>33</v>
+      </c>
+      <c r="G153" t="s">
+        <v>212</v>
+      </c>
+      <c r="H153" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154" t="s">
+        <v>31</v>
+      </c>
+      <c r="C154" t="s">
+        <v>26</v>
+      </c>
+      <c r="D154" t="n">
+        <v>8591</v>
+      </c>
+      <c r="E154" t="s">
+        <v>32</v>
+      </c>
+      <c r="F154" t="s">
+        <v>33</v>
+      </c>
+      <c r="G154" t="s">
+        <v>34</v>
+      </c>
+      <c r="H154" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>5</v>
+      </c>
+      <c r="B155" t="s">
+        <v>19</v>
+      </c>
+      <c r="C155" t="s">
+        <v>26</v>
+      </c>
+      <c r="D155" t="n">
+        <v>9368</v>
+      </c>
+      <c r="E155" t="s">
+        <v>21</v>
+      </c>
+      <c r="F155" t="s">
+        <v>22</v>
+      </c>
+      <c r="G155" t="s">
+        <v>23</v>
+      </c>
+      <c r="H155" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>3</v>
+      </c>
+      <c r="B156" t="s">
+        <v>271</v>
+      </c>
+      <c r="C156" t="s">
+        <v>26</v>
+      </c>
+      <c r="D156" t="n">
+        <v>9640</v>
+      </c>
+      <c r="E156" t="s">
+        <v>86</v>
+      </c>
+      <c r="F156" t="s">
+        <v>33</v>
+      </c>
+      <c r="G156" t="s">
+        <v>163</v>
+      </c>
+      <c r="H156" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>7</v>
+      </c>
+      <c r="B157" t="s">
+        <v>208</v>
+      </c>
+      <c r="C157" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157" t="n">
+        <v>10320</v>
+      </c>
+      <c r="E157" t="s">
+        <v>76</v>
+      </c>
+      <c r="F157" t="s">
+        <v>33</v>
+      </c>
+      <c r="G157" t="s">
+        <v>82</v>
+      </c>
+      <c r="H157" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>6</v>
+      </c>
+      <c r="B158" t="s">
+        <v>208</v>
+      </c>
+      <c r="C158" t="s">
+        <v>26</v>
+      </c>
+      <c r="D158" t="n">
+        <v>10363</v>
+      </c>
+      <c r="E158" t="s">
+        <v>76</v>
+      </c>
+      <c r="F158" t="s">
+        <v>33</v>
+      </c>
+      <c r="G158" t="s">
+        <v>82</v>
+      </c>
+      <c r="H158" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>3</v>
+      </c>
+      <c r="B159" t="s">
+        <v>36</v>
+      </c>
+      <c r="C159" t="s">
+        <v>20</v>
+      </c>
+      <c r="D159" t="n">
+        <v>10459</v>
+      </c>
+      <c r="E159" t="s">
+        <v>37</v>
+      </c>
+      <c r="F159" t="s">
+        <v>33</v>
+      </c>
+      <c r="G159" t="s">
+        <v>38</v>
+      </c>
+      <c r="H159" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>5</v>
+      </c>
+      <c r="B160" t="s">
+        <v>39</v>
+      </c>
+      <c r="C160" t="s">
+        <v>20</v>
+      </c>
+      <c r="D160" t="n">
+        <v>10702</v>
+      </c>
+      <c r="E160" t="s">
         <v>40</v>
       </c>
-      <c r="E66" t="n">
-        <v>13</v>
-      </c>
-      <c r="F66" t="s">
-        <v>48</v>
+      <c r="F160" t="s">
+        <v>33</v>
+      </c>
+      <c r="G160" t="s">
+        <v>41</v>
+      </c>
+      <c r="H160" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>4</v>
+      </c>
+      <c r="B161" t="s">
+        <v>39</v>
+      </c>
+      <c r="C161" t="s">
+        <v>26</v>
+      </c>
+      <c r="D161" t="n">
+        <v>11928</v>
+      </c>
+      <c r="E161" t="s">
+        <v>40</v>
+      </c>
+      <c r="F161" t="s">
+        <v>33</v>
+      </c>
+      <c r="G161" t="s">
+        <v>41</v>
+      </c>
+      <c r="H161" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C162" t="s">
+        <v>26</v>
+      </c>
+      <c r="D162" t="n">
+        <v>12137</v>
+      </c>
+      <c r="E162" t="s">
+        <v>37</v>
+      </c>
+      <c r="F162" t="s">
+        <v>33</v>
+      </c>
+      <c r="G162" t="s">
+        <v>38</v>
+      </c>
+      <c r="H162" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" t="s">
+        <v>31</v>
+      </c>
+      <c r="C163" t="s">
+        <v>20</v>
+      </c>
+      <c r="D163" t="n">
+        <v>13825</v>
+      </c>
+      <c r="E163" t="s">
+        <v>32</v>
+      </c>
+      <c r="F163" t="s">
+        <v>33</v>
+      </c>
+      <c r="G163" t="s">
+        <v>34</v>
+      </c>
+      <c r="H163" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>4</v>
+      </c>
+      <c r="B164" t="s">
+        <v>25</v>
+      </c>
+      <c r="C164" t="s">
+        <v>26</v>
+      </c>
+      <c r="D164" t="n">
+        <v>14114</v>
+      </c>
+      <c r="E164" t="s">
+        <v>27</v>
+      </c>
+      <c r="F164" t="s">
+        <v>28</v>
+      </c>
+      <c r="G164" t="s">
+        <v>29</v>
+      </c>
+      <c r="H164" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>3</v>
+      </c>
+      <c r="B165" t="s">
+        <v>19</v>
+      </c>
+      <c r="C165" t="s">
+        <v>20</v>
+      </c>
+      <c r="D165" t="n">
+        <v>14227</v>
+      </c>
+      <c r="E165" t="s">
+        <v>21</v>
+      </c>
+      <c r="F165" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" t="s">
+        <v>23</v>
+      </c>
+      <c r="H165" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
